--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,403 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>633200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>719300</v>
+      </c>
+      <c r="F8" s="3">
         <v>648700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>650200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>610500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>683600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>662100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>635400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>609200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>599200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>646900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>589500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>526600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>558500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>538200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>529500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>494900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>585500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>559700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>551100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>497900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>569300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>581200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>553700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>550400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>573900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>589400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>496100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>407500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>284800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>335200</v>
+      </c>
+      <c r="F9" s="3">
         <v>288400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>298000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>281600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>320400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>296500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>277800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>269000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>268100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>281600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>251800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>236600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>261700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>257400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>239900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>231700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>266500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>257100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>249600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>228900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>261400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>260800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>246700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>249500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>261900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>263200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>220600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>182300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>348400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>384100</v>
+      </c>
+      <c r="F10" s="3">
         <v>360300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>352200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>328900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>363200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>365600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>357600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>340200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>331100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>365300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>337700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>290000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>296800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>280800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>289600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>263200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>319000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>302600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>301500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>269000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>307900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>320400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>307000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>300900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>312000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>326200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>275500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>225200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,52 +1296,58 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>87400</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>87400</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1315,44 +1355,50 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>1200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1500</v>
-      </c>
       <c r="W14" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>1500</v>
       </c>
       <c r="Y14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>473800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>534300</v>
+      </c>
+      <c r="F17" s="3">
         <v>477700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>477700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>466300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>506000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>477200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>451400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>453300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>447800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>458600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>423100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>417500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>521200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>426100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>404400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>419800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>445800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>429500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>422200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>413600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>452500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>443700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>422300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>431100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>449200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>436000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>392600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>331600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>159400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>185000</v>
+      </c>
+      <c r="F18" s="3">
         <v>171000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>172500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>144200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>177600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>184900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>184000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>155900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>151400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>188300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>166400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>109100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>37300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>112100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>125100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>75100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>139700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>130200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>128900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>84300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>116800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>137500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>131400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>119300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>124800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>153400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>103500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>75900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,453 +1747,485 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>5600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-39300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-4200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-3900</v>
       </c>
       <c r="W20" s="3">
         <v>-200</v>
       </c>
       <c r="X20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>193700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>218800</v>
+      </c>
+      <c r="F21" s="3">
         <v>201200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>198600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>168000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>207900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>211100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>169600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>183000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>171000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>213400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>188300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>130800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>62300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>131300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>151900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>101500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>165100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>158800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>156400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>108200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>143900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>163800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>157700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>141100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>150100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>179700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>123400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>94500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F22" s="3">
         <v>12100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>10500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>5400</v>
       </c>
       <c r="J22" s="3">
         <v>5700</v>
       </c>
       <c r="K22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="M22" s="3">
         <v>5300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>6100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>7100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>6800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>7300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>8300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>9700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>10900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>11500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>12400</v>
-      </c>
-      <c r="V22" s="3">
-        <v>12400</v>
       </c>
       <c r="W22" s="3">
         <v>12400</v>
       </c>
       <c r="X22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>13800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>12100</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>11300</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>11700</v>
       </c>
       <c r="AB22" s="3">
         <v>11300</v>
       </c>
       <c r="AC22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AE22" s="3">
         <v>7900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>5600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>160600</v>
+      </c>
+      <c r="F23" s="3">
         <v>162100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>161600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>131100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>177500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>180500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>139300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>152000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>140100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>180400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>155900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>97800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>95500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>116600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>63100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>127300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>119500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>116300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>68000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>104200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>122700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>118100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>103500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>112900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>142500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>94600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>70400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>32800</v>
+      </c>
+      <c r="F24" s="3">
         <v>34200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>34100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>26800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>36300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>38700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>29600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>31600</v>
       </c>
       <c r="K24" s="3">
         <v>29600</v>
       </c>
       <c r="L24" s="3">
+        <v>31600</v>
+      </c>
+      <c r="M24" s="3">
+        <v>29600</v>
+      </c>
+      <c r="N24" s="3">
         <v>38200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>31700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>20200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>8500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>24500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>11100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>24600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>25600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>24400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>14600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>16900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>27800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>26900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>33000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>41000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>30100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>20400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>127800</v>
+      </c>
+      <c r="F26" s="3">
         <v>127900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>127600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>104300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>141200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>141800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>109600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>120400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>110500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>142200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>124100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>77600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>18500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>87000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>92100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>52000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>102700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>93900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>91900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>53400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>87300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>94900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>91200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>104600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>79800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>101500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>64500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>50000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>127800</v>
+      </c>
+      <c r="F27" s="3">
         <v>127900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>127600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>104300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>141200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>141800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>109600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>120400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>110500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>142200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>124100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>77600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>18500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>87000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>92100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>52000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>102700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>93900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>91900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>53400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>87300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>94900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>91200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>104600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>79800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>101500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>64500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>50000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,44 +2645,44 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-4900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-600</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>22100</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2571,8 +2693,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-5600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>39300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>4200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>9300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
-      </c>
-      <c r="U32" s="3">
-        <v>200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>3900</v>
       </c>
       <c r="W32" s="3">
         <v>200</v>
       </c>
       <c r="X32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>4500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>127800</v>
+      </c>
+      <c r="F33" s="3">
         <v>127900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>127600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>104300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>141200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>141800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>109600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>120400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>110500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>142200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>124100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>77600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>18500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>87000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>92100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>52000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>102700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>93900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>91900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>48600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>86700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>94900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>91200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>126600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>79800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>101500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>64500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>50000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>127800</v>
+      </c>
+      <c r="F35" s="3">
         <v>127900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>127600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>104300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>141200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>141800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>109600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>120400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>110500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>142200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>124100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>77600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>18500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>87000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>92100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>52000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>102700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>93900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>91900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>48600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>86700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>94900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>91200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>126600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>79800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>101500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>64500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>50000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>115700</v>
+      </c>
+      <c r="F41" s="3">
         <v>143100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>129100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>122000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>163500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>128700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>120900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>170500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>300000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>174200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>133300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>225700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>208300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>221800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>306300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>115100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>151200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>147800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>149200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>85500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>95700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>266800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>155900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>132800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>90400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>110700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>88400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>87700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,364 +3623,394 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>537700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>590900</v>
+      </c>
+      <c r="F43" s="3">
         <v>533800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>527900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>546600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>537300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>530800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>499500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>465700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>489400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>516700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>470600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>455400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>471900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>498300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>474900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>471600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>530800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>500000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>489700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>463200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>491400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>507700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>512400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>488300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>505100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>498800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>428700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>358400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>451200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>454800</v>
+      </c>
+      <c r="F44" s="3">
         <v>439700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>440200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>447700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>383400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>399600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>383200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>366400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>327200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>304000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>295800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>282400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>277000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>310600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>312100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>294800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>283400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>282600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>280700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>271200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>264500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>271400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>284400</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>275700</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>264300</v>
       </c>
       <c r="AB44" s="3">
         <v>275700</v>
       </c>
       <c r="AC44" s="3">
+        <v>264300</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>275700</v>
+      </c>
+      <c r="AE44" s="3">
         <v>275800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>241300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F45" s="3">
         <v>60200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>58300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>62000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>48800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>56500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>56200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>51600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>48300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>50900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>49600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>64600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>63400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>50100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>50000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>48800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>45900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>50300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>45300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>47300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>32500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>32000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>31300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>31200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>28600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>34900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>35900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>32700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1208100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1229300</v>
+      </c>
+      <c r="F46" s="3">
         <v>1176900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1155400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1178400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1133000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1115600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1059800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1054200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1164800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1045800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>949400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1028100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1020600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1080700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1143300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>930300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1011200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>980700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>964900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>867200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>884100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1077800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>984000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>928000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>888400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>920200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>828800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>720000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,186 +4098,204 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>499800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>499000</v>
+      </c>
+      <c r="F48" s="3">
         <v>455300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>462000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>472800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>455700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>459700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>463500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>473300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>466400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>473800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>482300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>481700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>480700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>547000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>526200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>530700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>398900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>392000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>386300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>387700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>386700</v>
-      </c>
-      <c r="X48" s="3">
-        <v>356800</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>359500</v>
       </c>
       <c r="Z48" s="3">
         <v>356800</v>
       </c>
       <c r="AA48" s="3">
+        <v>359500</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>356800</v>
+      </c>
+      <c r="AC48" s="3">
         <v>346400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>335700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>320000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>269800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3471600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3456900</v>
+      </c>
+      <c r="F49" s="3">
         <v>2461300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2474900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2484900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2134100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2157000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2179000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2210600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2070500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2089300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2104800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2119800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2120900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2137700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2028200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2045400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2060300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2072500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2078700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2097700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2107800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2126600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2148300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4478,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>66500</v>
+      </c>
+      <c r="F52" s="3">
         <v>103500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>100800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>101200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>97600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>91500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>93900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>96800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>89200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>61200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>58300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>53800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>52400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>54500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>45200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>44500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>46000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>46300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>45100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>45100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>42500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>46200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>47400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>45700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>43400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>57200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>55900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>34900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5247100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5251800</v>
+      </c>
+      <c r="F54" s="3">
         <v>4197000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4193100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4237400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3820400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3823800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3796300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3835000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3791000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3670100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3594900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3683400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3674700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3820000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3742900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3550900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3516400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3491500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3475100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3397700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3421000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3607400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3539200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,542 +4837,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>106300</v>
+      </c>
+      <c r="F57" s="3">
         <v>105100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>85400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>90600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>99300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>100400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>96900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>96500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>91700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>92900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>84800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>74100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>70900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>71400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>79800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>78100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>85100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>85600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>93000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>81000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>83600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>80800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>86800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>82100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>86000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>80700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>85200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>74000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>120600</v>
+      </c>
+      <c r="F58" s="3">
         <v>115200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>608000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>425800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>397400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>407000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>316200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>39900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>40000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>37200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>44100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>44100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>44000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>49800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>49800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>49300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>174100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>173500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>158400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>58400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>33300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>38600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>231500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>331700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>331400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>132200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>145500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>46600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>326900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>355200</v>
+      </c>
+      <c r="F59" s="3">
         <v>308400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>297000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>309000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>337500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>319900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>309400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>293100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>313700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>290700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>256300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>241300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>248100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>226000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>230600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>216000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>218400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>185200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>195100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>185100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>233400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>221700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>216400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>196000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>230300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>224400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>225800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>169600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>551700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>582100</v>
+      </c>
+      <c r="F60" s="3">
         <v>528600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>990400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>825500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>834200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>827300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>722500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>429500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>445400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>420800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>385300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>359600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>363100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>347200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>360200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>343300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>477600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>444200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>446500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>324500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>350300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>341100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>534700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>609800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>647700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>437400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>456500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>290200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1525700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1633100</v>
+      </c>
+      <c r="F61" s="3">
         <v>738000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>356600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>606200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>356500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>415200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>493200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>787900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>796700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>804800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>845000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>992100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1078400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1232100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1248300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1084400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1084900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1179900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1220400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1331400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1294200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1521400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1312500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>912400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>445700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>438600</v>
+      </c>
+      <c r="F62" s="3">
         <v>350700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>349200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>359000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>335300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>382300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>390100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>399000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>389800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>381300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>414300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>474500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>474200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>470800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>481900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>488900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>372900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>320600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>336900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>340300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>325800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>322000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>329200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>336900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>345200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>369000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>386300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>296600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2523100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2653700</v>
+      </c>
+      <c r="F66" s="3">
         <v>1617200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1696100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1790700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1526000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1624800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1605700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1616400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1631800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1606900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1644600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1826200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1915700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2050000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2090400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1916600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1935400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1944700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2003800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1996200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1970300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2184500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2176300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4060100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3989400</v>
+      </c>
+      <c r="F72" s="3">
         <v>3900400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3809600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3719300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3652200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3548200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3435800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3355700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3265000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3184200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3064700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2963300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2908700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2912800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2847800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2776700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2747700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2666800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2593000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2521100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2488400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2403200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2325700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2598100</v>
+      </c>
+      <c r="F76" s="3">
         <v>2579800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2497000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2446700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2294400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2199000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2190600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2218600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2159100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2063200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1950400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1857200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1759000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1769900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1652500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1634300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1581000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1546900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1471300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1401500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1450700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1422900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1362900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>962300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>893800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>127800</v>
+      </c>
+      <c r="F81" s="3">
         <v>127900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>127600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>104300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>141200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>141800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>109600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>120400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>110500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>142200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>124100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>77600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>18500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>87000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>92100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>52000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>102700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>93900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>91900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>48600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>86700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>94900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>91200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>126600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>79800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>101500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>64500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>50000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7002,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>31300</v>
+      </c>
+      <c r="F83" s="3">
         <v>27100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>27100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>26400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>24700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>24900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>25000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>25400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>25700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>26900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>25300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>26000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>29100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>28500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>27000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>28600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>26900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>27800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>27700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>27700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>27400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>27300</v>
       </c>
       <c r="Y83" s="3">
         <v>27400</v>
       </c>
       <c r="Z83" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>27400</v>
+      </c>
+      <c r="AB83" s="3">
         <v>26300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>25500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>26000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>20900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>18500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>172400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>163200</v>
+      </c>
+      <c r="F89" s="3">
         <v>190200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>164600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>123300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>173400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>125200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>96400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>118100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>170500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>127700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>104400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>143300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>192500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>91800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>101900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>116300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>146500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>74500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>105100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>56800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>161700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>130600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>103000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>109300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>135000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>82400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>58200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>81200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7702,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-9300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-12100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-14600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-12500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-10800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-14400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-12000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-13900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-18200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-19400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-12500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-14100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-43800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1034900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-387100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-12200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-14200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-184100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-7900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-30900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-135500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-13900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-13800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-18400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-32200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-11800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-13900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-48900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-17100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,97 +8117,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="F96" s="3">
         <v>-37100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-37300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-37200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-37200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-29400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-29600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-29700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-29700</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-22700</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-22700</v>
       </c>
       <c r="N96" s="3">
         <v>-22700</v>
       </c>
       <c r="O96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="P96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-22600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-21900</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-22000</v>
       </c>
       <c r="R96" s="3">
         <v>-21900</v>
       </c>
       <c r="S96" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="T96" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="U96" s="3">
         <v>-21800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-20100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-20000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-20200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-20300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8493,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-140500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>852600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-166900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-150900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>215700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-121600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-101500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-131000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-61900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-34800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-77800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-188100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-122300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-176100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-44400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>107200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-138200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-121500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-43000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-31300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-55300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-280200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-60300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>749100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-4100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-3700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>4900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>3200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="F102" s="3">
         <v>14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-41500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>34700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-49600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-129400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>125700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>40900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-92400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>17400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-13500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>191200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-36100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>63600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-10100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-171100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>110900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>23100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>42500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>22300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>20400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,239 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>650600</v>
+      </c>
+      <c r="E8" s="3">
         <v>633200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>719300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>648700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>650200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>610500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>683600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>662100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>635400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>609200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>599200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>646900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>589500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>526600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>558500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>538200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>529500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>494900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>585500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>559700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>551100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>497900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>569300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>581200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>553700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>550400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>573900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>589400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>496100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>407500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -896,189 +902,195 @@
         <v>284800</v>
       </c>
       <c r="E9" s="3">
+        <v>284800</v>
+      </c>
+      <c r="F9" s="3">
         <v>335200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>288400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>298000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>281600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>320400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>296500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>277800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>269000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>268100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>281600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>251800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>236600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>261700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>257400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>239900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>231700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>266500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>257100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>249600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>228900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>261400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>260800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>246700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>249500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>261900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>263200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>220600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>182300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>365800</v>
+      </c>
+      <c r="E10" s="3">
         <v>348400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>384100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>360300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>352200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>328900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>363200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>365600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>357600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>340200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>331100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>365300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>337700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>290000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>296800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>280800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>289600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>263200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>319000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>302600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>301500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>269000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>307900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>320400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>307000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>300900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>312000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>326200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>275500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>225200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1328,17 +1347,17 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1346,11 +1365,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>87400</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1361,44 +1380,47 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E17" s="3">
         <v>473800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>534300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>477700</v>
       </c>
       <c r="G17" s="3">
         <v>477700</v>
       </c>
       <c r="H17" s="3">
+        <v>477700</v>
+      </c>
+      <c r="I17" s="3">
         <v>466300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>506000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>477200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>451400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>453300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>447800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>458600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>423100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>417500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>521200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>426100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>404400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>419800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>445800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>429500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>422200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>413600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>452500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>443700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>422300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>431100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>449200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>436000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>392600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>331600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E18" s="3">
         <v>159400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>185000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>171000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>172500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>144200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>177600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>184900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>184000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>155900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>151400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>188300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>166400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>109100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>112100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>125100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>75100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>139700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>130200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>128900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>84300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>116800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>137500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>131400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>119300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>124800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>153400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>103500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>75900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,260 +1781,267 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-39300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E21" s="3">
         <v>193700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>218800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>201200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>198600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>168000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>207900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>211100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>169600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>183000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>171000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>213400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>188300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>130800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>62300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>131300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>151900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>101500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>165100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>158800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>156400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>108200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>143900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>163800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>157700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>141100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>150100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>179700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>123400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>94500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E22" s="3">
         <v>21400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>5700</v>
       </c>
       <c r="J22" s="3">
         <v>5700</v>
       </c>
       <c r="K22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="L22" s="3">
         <v>5400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11500</v>
-      </c>
-      <c r="W22" s="3">
-        <v>12400</v>
       </c>
       <c r="X22" s="3">
         <v>12400</v>
@@ -2011,221 +2050,230 @@
         <v>12400</v>
       </c>
       <c r="Z22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AA22" s="3">
         <v>13800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>149300</v>
+      </c>
+      <c r="E23" s="3">
         <v>138700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>160600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>162100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>161600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>131100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>177500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>180500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>139300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>152000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>140100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>180400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>155900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>97800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>95500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>116600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>63100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>127300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>119500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>116300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>68000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>104200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>122700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>118100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>103500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>112900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>142500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>94600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>70400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E24" s="3">
         <v>29100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>32800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>34200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>36300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>38700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>29600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>38200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>24600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>25600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>24400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>26900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>33000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>41000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>30100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>20400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E26" s="3">
         <v>109600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>127800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>127900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>127600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>104300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>141200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>141800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>109600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>120400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>110500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>142200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>124100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>77600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>87000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>92100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>52000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>102700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>93900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>91900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>53400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>87300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>94900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>91200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>104600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>79800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>101500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>64500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>50000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E27" s="3">
         <v>109600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>127800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>127900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>127600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>104300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>141200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>141800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>109600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>120400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>110500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>142200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>124100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>77600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>87000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>92100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>52000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>102700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>93900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>91900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>53400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>87300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>94900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>91200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>104600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>79800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>101500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>64500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>50000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2651,8 +2711,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2660,8 +2720,8 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2670,22 +2730,22 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-600</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>22100</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>39300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E33" s="3">
         <v>109600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>127800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>127900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>127600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>104300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>141200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>141800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>109600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>120400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>110500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>142200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>124100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>77600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>87000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>92100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>52000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>102700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>93900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>91900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>48600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>86700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>94900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>91200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>126600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>79800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>101500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>64500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>50000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E35" s="3">
         <v>109600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>127800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>127900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>127600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>104300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>141200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>141800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>109600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>120400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>110500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>142200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>124100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>77600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>87000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>92100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>52000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>102700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>93900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>91900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>48600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>86700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>94900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>91200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>126600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>79800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>101500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>64500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>50000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E41" s="3">
         <v>136200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>115700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>143100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>163500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>128700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>120900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>170500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>300000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>174200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>225700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>208300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>221800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>306300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>115100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>151200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>147800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>149200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>85500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>95700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>266800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>155900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>132800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>90400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>110700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>88400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>87700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,388 +3718,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>530300</v>
+      </c>
+      <c r="E43" s="3">
         <v>537700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>590900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>533800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>527900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>546600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>537300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>530800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>499500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>465700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>489400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>516700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>470600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>455400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>471900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>498300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>474900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>471600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>530800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>500000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>489700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>463200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>491400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>507700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>512400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>488300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>505100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>498800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>428700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>358400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E44" s="3">
         <v>451200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>454800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>439700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>440200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>447700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>383400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>399600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>383200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>366400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>327200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>304000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>295800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>282400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>277000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>310600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>312100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>294800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>283400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>282600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>280700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>271200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>264500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>271400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>284400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>275700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>264300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>275700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>275800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>241300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E45" s="3">
         <v>83000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>68000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>60200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>58300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>62000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>56500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>51600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>50900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>49600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>64600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>63400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>50100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>50000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>45900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>50300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>45300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>47300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>32500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>32000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>31300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>28600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>34900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>35900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>32700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1185600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1208100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1229300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1176900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1155400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1178400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1133000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1115600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1059800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1054200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1164800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1045800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>949400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1028100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1020600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1080700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1143300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>930300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1011200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>980700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>964900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>867200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>884100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1077800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>984000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>928000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>888400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>920200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>828800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>720000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>492400</v>
+      </c>
+      <c r="E48" s="3">
         <v>499800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>499000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>455300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>462000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>472800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>455700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>459700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>463500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>473300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>466400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>473800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>482300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>481700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>480700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>547000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>526200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>530700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>398900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>392000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>386300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>387700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>386700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>356800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>359500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>356800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>346400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>335700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>320000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>269800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3425300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3471600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3456900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2461300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2474900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2484900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2134100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2157000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2179000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2210600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2070500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2089300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2104800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2119800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2120900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2137700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2028200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2045400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2060300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2072500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2078700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2097700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2107800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2126600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2148300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E52" s="3">
         <v>67600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>66500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>103500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>101200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>97600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>91500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>93900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>96800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>89200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>61200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>53800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>52400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>54500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>45200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>44500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>46000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>46300</v>
-      </c>
-      <c r="W52" s="3">
-        <v>45100</v>
       </c>
       <c r="X52" s="3">
         <v>45100</v>
       </c>
       <c r="Y52" s="3">
+        <v>45100</v>
+      </c>
+      <c r="Z52" s="3">
         <v>42500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>46200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>47400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>45700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>43400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>57200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>55900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>34900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5171900</v>
+      </c>
+      <c r="E54" s="3">
         <v>5247100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5251800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4197000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4193100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4237400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3820400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3823800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3796300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3835000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3791000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3670100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3594900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3683400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3674700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3820000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3742900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3550900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3516400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3491500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3475100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3397700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3421000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3607400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3539200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4848,569 +4978,587 @@
         <v>103200</v>
       </c>
       <c r="E57" s="3">
+        <v>103200</v>
+      </c>
+      <c r="F57" s="3">
         <v>106300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>105100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>85400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>90600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>99300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>96900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>96500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>91700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>92900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>84800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>70900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>71400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>79800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>78100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>85100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>85600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>93000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>81000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>83600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>80800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>86800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>82100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>86000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>80700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>85200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>74000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E58" s="3">
         <v>121600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>120600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>115200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>608000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>425800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>397400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>407000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>316200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>39900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>40000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>37200</v>
-      </c>
-      <c r="O58" s="3">
-        <v>44100</v>
       </c>
       <c r="P58" s="3">
         <v>44100</v>
       </c>
       <c r="Q58" s="3">
+        <v>44100</v>
+      </c>
+      <c r="R58" s="3">
         <v>44000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>49800</v>
       </c>
       <c r="S58" s="3">
         <v>49800</v>
       </c>
       <c r="T58" s="3">
+        <v>49800</v>
+      </c>
+      <c r="U58" s="3">
         <v>49300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>174100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>173500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>158400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>58400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>33300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>38600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>231500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>331700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>331400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>132200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>145500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>46600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>308200</v>
+      </c>
+      <c r="E59" s="3">
         <v>326900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>355200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>308400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>297000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>309000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>337500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>319900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>309400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>293100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>313700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>290700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>256300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>241300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>248100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>226000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>230600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>216000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>218400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>185200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>195100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>185100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>233400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>221700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>216400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>196000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>230300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>224400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>225800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>169600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E60" s="3">
         <v>551700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>582100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>528600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>990400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>825500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>834200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>827300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>722500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>429500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>445400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>420800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>385300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>359600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>363100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>347200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>360200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>343300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>477600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>444200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>446500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>324500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>350300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>341100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>534700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>609800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>647700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>437400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>456500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>290200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1426700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1525700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1633100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>738000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>356600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>606200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>356500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>415200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>493200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>787900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>796700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>804800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>845000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>992100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1078400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1232100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1248300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1084400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1084900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1179900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1220400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1331400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1294200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1521400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1312500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>912400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>420900</v>
+      </c>
+      <c r="E62" s="3">
         <v>445700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>438600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>350700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>349200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>359000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>335300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>382300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>390100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>399000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>389800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>381300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>414300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>474500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>474200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>470800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>481900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>488900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>372900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>320600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>336900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>340300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>325800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>322000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>329200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>336900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>345200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>369000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>386300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>296600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2383600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2523100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2653700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1617200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1696100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1790700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1526000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1624800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1605700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1616400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1631800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1606900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1644600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1826200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1915700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2050000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2090400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1916600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1935400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1944700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2003800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1996200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1970300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2184500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2176300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4139300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4060100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3989400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3900400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3809600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3719300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3652200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3548200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3435800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3355700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3265000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3184200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3064700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2963300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2908700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2912800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2847800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2776700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2747700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2666800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2593000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2521100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2488400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2403200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2325700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2788300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2724000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2598100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2579800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2497000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2446700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2294400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2199000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2190600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2218600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2159100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2063200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1950400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1857200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1759000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1769900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1652500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1634300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1581000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1546900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1471300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1401500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1450700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1422900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1362900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>962300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>893800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E81" s="3">
         <v>109600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>127800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>127900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>127600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>104300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>141200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>141800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>109600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>120400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>110500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>142200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>124100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>77600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>87000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>92100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>52000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>102700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>93900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>91900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>48600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>86700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>94900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>91200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>126600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>79800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>101500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>64500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>50000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E83" s="3">
         <v>33500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>31300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>27100</v>
       </c>
       <c r="G83" s="3">
         <v>27100</v>
       </c>
       <c r="H83" s="3">
+        <v>27100</v>
+      </c>
+      <c r="I83" s="3">
         <v>26400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>28600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>26900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27800</v>
-      </c>
-      <c r="W83" s="3">
-        <v>27700</v>
       </c>
       <c r="X83" s="3">
         <v>27700</v>
       </c>
       <c r="Y83" s="3">
+        <v>27700</v>
+      </c>
+      <c r="Z83" s="3">
         <v>27400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>27300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>26300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>25500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>26000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E89" s="3">
         <v>172400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>163200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>190200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>164600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>123300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>173400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>125200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>96400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>118100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>170500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>127700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>104400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>143300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>192500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>91800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>101900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>116300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>146500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>74500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>105100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>56800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>161700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>130600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>103000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>109300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>135000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>82400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>58200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>81200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1034900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-387100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-184100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-135500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-32200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-48900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-59900</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-22100</v>
       </c>
       <c r="AD94" s="3">
         <v>-22100</v>
       </c>
       <c r="AE94" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8128,34 +8361,34 @@
         <v>-38900</v>
       </c>
       <c r="E96" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="F96" s="3">
         <v>-38800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-37100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-37300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-37200</v>
       </c>
       <c r="I96" s="3">
         <v>-37200</v>
       </c>
       <c r="J96" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-29400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-29600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-29700</v>
       </c>
       <c r="M96" s="3">
         <v>-29700</v>
       </c>
       <c r="N96" s="3">
-        <v>-22700</v>
+        <v>-29700</v>
       </c>
       <c r="O96" s="3">
         <v>-22700</v>
@@ -8164,58 +8397,61 @@
         <v>-22700</v>
       </c>
       <c r="Q96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="R96" s="3">
         <v>-22600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-21900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-22000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-21900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-21800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-20100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-20000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-20200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-20300</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-17400</v>
       </c>
       <c r="AA96" s="3">
         <v>-17400</v>
       </c>
       <c r="AB96" s="3">
-        <v>-17300</v>
+        <v>-17400</v>
       </c>
       <c r="AC96" s="3">
         <v>-17300</v>
       </c>
       <c r="AD96" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-15600</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-15500</v>
       </c>
       <c r="AF96" s="3">
         <v>-15500</v>
       </c>
       <c r="AG96" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-125300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-140500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>852600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-166900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-150900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>215700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-121600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-101500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-131000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-61900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-34800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-77800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-188100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-122300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-176100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-44400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>107200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-138200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-121500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-43000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-31300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-280200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>749100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E102" s="3">
         <v>20500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-27500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-41500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-49600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-129400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>125700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>40900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-92400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-84500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>191200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-36100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>63600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-171100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>110900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>23100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>42500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>22300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>661600</v>
+      </c>
+      <c r="E8" s="3">
         <v>650600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>633200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>719300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>648700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>650200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>610500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>683600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>662100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>635400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>609200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>599200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>646900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>589500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>526600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>558500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>538200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>529500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>494900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>585500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>559700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>551100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>497900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>569300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>581200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>553700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>550400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>573900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>589400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>496100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>407500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>284800</v>
+        <v>292600</v>
       </c>
       <c r="E9" s="3">
         <v>284800</v>
       </c>
       <c r="F9" s="3">
+        <v>284800</v>
+      </c>
+      <c r="G9" s="3">
         <v>335200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>288400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>298000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>281600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>320400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>296500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>277800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>269000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>268100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>281600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>251800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>236600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>261700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>257400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>239900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>231700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>266500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>257100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>249600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>228900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>261400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>260800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>246700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>249500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>261900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>263200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>220600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>182300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E10" s="3">
         <v>365800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>348400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>384100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>360300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>352200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>328900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>363200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>365600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>357600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>340200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>331100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>365300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>337700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>290000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>296800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>280800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>289600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>263200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>319000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>302600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>301500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>269000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>307900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>320400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>307000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>300900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>312000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>326200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>275500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>225200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1350,17 +1370,17 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1368,11 +1388,11 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>87400</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1383,44 +1403,47 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>494500</v>
+      </c>
+      <c r="E17" s="3">
         <v>482000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>473800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>534300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>477700</v>
       </c>
       <c r="H17" s="3">
         <v>477700</v>
       </c>
       <c r="I17" s="3">
+        <v>477700</v>
+      </c>
+      <c r="J17" s="3">
         <v>466300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>506000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>477200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>451400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>453300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>447800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>458600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>423100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>417500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>521200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>426100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>404400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>419800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>445800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>429500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>422200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>413600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>452500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>443700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>422300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>431100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>449200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>436000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>392600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>331600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E18" s="3">
         <v>168600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>159400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>185000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>171000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>172500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>144200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>177600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>184900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>184000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>155900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>151400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>188300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>166400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>109100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>112100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>125100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>75100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>139700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>130200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>128900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>84300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>116800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>137500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>131400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>119300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>124800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>153400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>103500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>75900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,269 +1815,276 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-39300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E21" s="3">
         <v>202100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>193700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>218800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>201200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>198600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>168000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>207900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>211100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>169600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>183000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>171000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>213400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>188300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>130800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>62300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>131300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>151900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>101500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>165100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>158800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>156400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>108200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>143900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>163800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>157700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>141100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>150100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>179700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>123400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>94500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E22" s="3">
         <v>20100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>5700</v>
       </c>
       <c r="K22" s="3">
         <v>5700</v>
       </c>
       <c r="L22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="M22" s="3">
         <v>5400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11500</v>
-      </c>
-      <c r="X22" s="3">
-        <v>12400</v>
       </c>
       <c r="Y22" s="3">
         <v>12400</v>
@@ -2053,227 +2093,236 @@
         <v>12400</v>
       </c>
       <c r="AA22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>13800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E23" s="3">
         <v>149300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>138700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>160600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>162100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>161600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>131100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>177500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>180500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>139300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>152000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>140100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>180400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>155900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>97800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>95500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>116600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>63100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>127300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>119500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>116300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>68000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>104200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>122700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>118100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>103500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>112900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>142500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>94600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>70400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E24" s="3">
         <v>31100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>32800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>34100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>36300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>38200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>24600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>25600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>24400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>27800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>26900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>33000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>41000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>30100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>20400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E26" s="3">
         <v>118200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>109600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>127800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>127900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>127600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>104300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>141200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>141800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>109600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>120400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>142200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>124100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>77600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>87000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>92100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>52000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>102700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>93900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>91900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>53400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>87300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>94900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>91200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>104600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>79800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>101500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>64500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>50000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E27" s="3">
         <v>118200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>109600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>127800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>127900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>127600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>104300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>141200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>141800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>109600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>120400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>110500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>142200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>124100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>77600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>87000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>92100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>52000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>102700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>93900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>91900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>53400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>87300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>94900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>91200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>104600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>79800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>101500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>64500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>50000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,8 +2775,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2723,8 +2784,8 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2733,22 +2794,22 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-600</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>22100</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>39300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E33" s="3">
         <v>118200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>109600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>127800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>127900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>127600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>104300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>141200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>141800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>109600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>120400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>110500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>142200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>124100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>77600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>87000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>92100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>52000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>102700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>93900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>91900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>48600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>86700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>94900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>91200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>126600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>79800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>101500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>64500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>50000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E35" s="3">
         <v>118200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>109600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>127800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>127900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>127600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>104300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>141200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>141800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>109600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>120400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>110500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>142200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>124100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>77600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>87000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>92100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>52000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>102700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>93900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>91900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>48600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>86700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>94900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>91200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>126600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>79800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>101500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>64500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>50000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>165300</v>
+      </c>
+      <c r="E41" s="3">
         <v>125400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>115700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>143100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>129100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>163500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>128700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>120900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>170500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>300000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>174200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>225700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>208300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>221800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>306300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>115100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>151200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>147800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>149200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>85500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>95700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>266800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>155900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>132800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>90400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>110700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>88400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>87700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>538500</v>
+      </c>
+      <c r="E43" s="3">
         <v>530300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>537700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>590900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>533800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>527900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>546600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>537300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>530800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>499500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>465700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>489400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>516700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>470600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>455400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>471900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>498300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>474900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>471600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>530800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>500000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>489700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>463200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>491400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>507700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>512400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>488300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>505100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>498800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>428700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>358400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>438200</v>
+      </c>
+      <c r="E44" s="3">
         <v>443600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>451200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>454800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>439700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>440200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>447700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>383400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>399600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>383200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>366400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>327200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>304000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>295800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>282400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>277000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>310600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>312100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>294800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>283400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>282600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>280700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>271200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>264500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>271400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>284400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>275700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>264300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>275700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>275800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>241300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E45" s="3">
         <v>86300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>83000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>68000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>60200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>62000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>50900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>49600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>64600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>63400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>50100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>50000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>47300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>32500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>32000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>31200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>28600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>34900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>35900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>32700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1224100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1185600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1208100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1229300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1176900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1155400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1178400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1133000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1115600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1059800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1054200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1164800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1045800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>949400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1028100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1020600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1080700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1143300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>930300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1011200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>980700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>964900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>867200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>884100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1077800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>984000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>928000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>888400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>920200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>828800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>720000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E48" s="3">
         <v>492400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>499800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>499000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>455300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>462000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>472800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>455700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>459700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>463500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>473300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>466400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>473800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>482300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>481700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>480700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>547000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>526200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>530700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>398900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>392000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>386300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>387700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>386700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>356800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>359500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>356800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>346400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>335700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>320000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>269800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3414500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3425300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3471600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3456900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2461300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2474900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2484900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2134100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2157000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2179000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2210600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2070500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2089300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2104800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2119800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2120900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2137700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2028200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2045400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2060300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2072500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2078700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2097700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2107800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2126600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2148300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E52" s="3">
         <v>68600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>66500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>103500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>100800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>101200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>97600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>91500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>93900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>96800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>89200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>61200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>58300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>53800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>54500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>45200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>44500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>46000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>46300</v>
-      </c>
-      <c r="X52" s="3">
-        <v>45100</v>
       </c>
       <c r="Y52" s="3">
         <v>45100</v>
       </c>
       <c r="Z52" s="3">
+        <v>45100</v>
+      </c>
+      <c r="AA52" s="3">
         <v>42500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>46200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>47400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>45700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>43400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>57200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>55900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>34900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5204400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5171900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5247100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5251800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4197000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4193100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4237400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3820400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3823800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3796300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3835000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3791000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3670100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3594900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3683400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3674700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3820000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3742900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3550900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3516400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3491500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3475100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3397700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3421000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3607400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3539200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>103200</v>
+        <v>98300</v>
       </c>
       <c r="E57" s="3">
         <v>103200</v>
       </c>
       <c r="F57" s="3">
+        <v>103200</v>
+      </c>
+      <c r="G57" s="3">
         <v>106300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>105100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>85400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>90600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>99300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>96900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>96500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>91700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>92900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>84800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>74100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>70900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>71400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>79800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>78100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>85100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>85600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>93000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>81000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>83600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>80800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>86800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>82100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>86000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>80700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>85200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>74000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E58" s="3">
         <v>124600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>121600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>120600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>115200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>608000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>425800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>397400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>407000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>316200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>39900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>40000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>37200</v>
-      </c>
-      <c r="P58" s="3">
-        <v>44100</v>
       </c>
       <c r="Q58" s="3">
         <v>44100</v>
       </c>
       <c r="R58" s="3">
+        <v>44100</v>
+      </c>
+      <c r="S58" s="3">
         <v>44000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>49800</v>
       </c>
       <c r="T58" s="3">
         <v>49800</v>
       </c>
       <c r="U58" s="3">
+        <v>49800</v>
+      </c>
+      <c r="V58" s="3">
         <v>49300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>174100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>173500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>158400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>58400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>33300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>38600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>231500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>331700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>331400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>132200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>145500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>46600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E59" s="3">
         <v>308200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>326900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>355200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>308400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>297000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>309000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>337500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>319900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>309400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>293100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>313700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>290700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>256300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>241300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>248100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>226000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>230600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>216000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>218400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>185200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>195100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>185100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>233400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>221700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>216400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>196000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>230300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>224400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>225800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>169600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>518300</v>
+      </c>
+      <c r="E60" s="3">
         <v>536000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>551700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>582100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>528600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>990400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>825500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>834200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>827300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>722500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>429500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>445400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>420800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>385300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>359600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>363100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>347200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>360200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>343300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>477600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>444200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>446500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>324500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>350300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>341100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>534700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>609800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>647700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>437400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>456500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>290200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1410600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1426700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1525700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1633100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>738000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>356600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>606200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>356500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>415200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>493200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>787900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>796700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>804800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>845000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>992100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1078400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1232100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1248300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1084400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1084900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1179900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1220400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1331400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1294200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1521400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1312500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>912400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>421700</v>
+      </c>
+      <c r="E62" s="3">
         <v>420900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>445700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>438600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>350700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>349200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>359000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>335300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>382300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>390100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>399000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>389800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>381300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>414300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>474500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>474200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>470800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>481900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>488900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>372900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>320600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>336900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>340300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>325800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>322000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>329200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>336900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>345200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>369000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>386300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>296600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2350600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2383600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2523100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2653700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1617200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1696100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1790700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1526000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1624800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1605700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1616400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1631800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1606900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1644600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1826200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1915700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2050000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2090400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1916600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1935400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1944700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2003800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1996200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1970300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2184500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2176300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4217700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4139300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4060100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3989400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3900400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3809600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3719300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3652200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3548200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3435800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3355700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3265000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3184200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3064700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2963300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2908700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2912800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2847800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2776700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2747700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2666800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2593000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2521100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2488400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2403200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2325700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2853800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2788300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2724000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2598100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2579800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2497000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2446700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2294400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2199000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2190600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2218600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2159100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2063200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1950400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1857200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1759000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1769900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1652500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1634300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1581000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1546900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1471300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1401500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1450700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1422900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1362900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>962300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>893800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E81" s="3">
         <v>118200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>109600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>127800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>127900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>127600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>104300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>141200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>141800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>109600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>120400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>110500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>142200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>124100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>77600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>87000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>92100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>52000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>102700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>93900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>91900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>48600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>86700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>94900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>91200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>126600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>79800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>101500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>64500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>50000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E83" s="3">
         <v>32700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>31300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>27100</v>
       </c>
       <c r="H83" s="3">
         <v>27100</v>
       </c>
       <c r="I83" s="3">
+        <v>27100</v>
+      </c>
+      <c r="J83" s="3">
         <v>26400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>26000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>29100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>28500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>28600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>26900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27800</v>
-      </c>
-      <c r="X83" s="3">
-        <v>27700</v>
       </c>
       <c r="Y83" s="3">
         <v>27700</v>
       </c>
       <c r="Z83" s="3">
+        <v>27700</v>
+      </c>
+      <c r="AA83" s="3">
         <v>27400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>27400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>26300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>25500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>26000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E89" s="3">
         <v>122600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>172400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>163200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>190200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>164600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>123300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>173400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>125200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>96400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>118100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>170500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>127700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>104400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>143300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>192500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>91800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>101900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>116300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>146500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>74500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>105100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>56800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>161700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>130600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>103000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>109300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>135000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>82400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>58200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>81200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1034900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-387100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-184100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-135500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-32200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-48900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-59900</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-22100</v>
       </c>
       <c r="AE94" s="3">
         <v>-22100</v>
       </c>
       <c r="AF94" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,46 +8585,47 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-38900</v>
+        <v>-39000</v>
       </c>
       <c r="E96" s="3">
         <v>-38900</v>
       </c>
       <c r="F96" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="G96" s="3">
         <v>-38800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-37100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-37300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-37200</v>
       </c>
       <c r="J96" s="3">
         <v>-37200</v>
       </c>
       <c r="K96" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="L96" s="3">
         <v>-29400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-29600</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-29700</v>
       </c>
       <c r="N96" s="3">
         <v>-29700</v>
       </c>
       <c r="O96" s="3">
-        <v>-22700</v>
+        <v>-29700</v>
       </c>
       <c r="P96" s="3">
         <v>-22700</v>
@@ -8400,58 +8634,61 @@
         <v>-22700</v>
       </c>
       <c r="R96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="S96" s="3">
         <v>-22600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-21900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-22000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-21900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-21800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-20100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-20200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-20300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-17400</v>
       </c>
       <c r="AB96" s="3">
         <v>-17400</v>
       </c>
       <c r="AC96" s="3">
-        <v>-17300</v>
+        <v>-17400</v>
       </c>
       <c r="AD96" s="3">
         <v>-17300</v>
       </c>
       <c r="AE96" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-15600</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-15500</v>
       </c>
       <c r="AG96" s="3">
         <v>-15500</v>
       </c>
       <c r="AH96" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-125300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-140500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>852600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-166900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-150900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>215700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-121600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-101500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-131000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-61900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-77800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-188100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-122300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-176100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-44400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>107200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-138200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-121500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-43000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-31300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-280200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>749100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-41500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>34700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-49600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-129400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>125700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-92400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-84500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>191200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-36100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>63600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-171100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>110900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>23100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>42500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>20400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -1010,7 +1010,7 @@
         <v>369000</v>
       </c>
       <c r="E10" s="3">
-        <v>365800</v>
+        <v>365900</v>
       </c>
       <c r="F10" s="3">
         <v>348400</v>
@@ -1022,7 +1022,7 @@
         <v>360300</v>
       </c>
       <c r="I10" s="3">
-        <v>352200</v>
+        <v>352100</v>
       </c>
       <c r="J10" s="3">
         <v>328900</v>
@@ -1153,8 +1153,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>71400</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1346,26 +1346,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1448,25 +1448,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>31300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>27100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>27100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1583,25 +1583,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>494500</v>
+        <v>493600</v>
       </c>
       <c r="E17" s="3">
-        <v>482000</v>
+        <v>481000</v>
       </c>
       <c r="F17" s="3">
-        <v>473800</v>
+        <v>472700</v>
       </c>
       <c r="G17" s="3">
-        <v>534300</v>
+        <v>534600</v>
       </c>
       <c r="H17" s="3">
-        <v>477700</v>
+        <v>476300</v>
       </c>
       <c r="I17" s="3">
-        <v>477700</v>
+        <v>476300</v>
       </c>
       <c r="J17" s="3">
-        <v>466300</v>
+        <v>464900</v>
       </c>
       <c r="K17" s="3">
         <v>506000</v>
@@ -1684,25 +1684,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>167100</v>
+        <v>168000</v>
       </c>
       <c r="E18" s="3">
-        <v>168600</v>
+        <v>169600</v>
       </c>
       <c r="F18" s="3">
-        <v>159400</v>
+        <v>160500</v>
       </c>
       <c r="G18" s="3">
-        <v>185000</v>
+        <v>184700</v>
       </c>
       <c r="H18" s="3">
-        <v>171000</v>
+        <v>172300</v>
       </c>
       <c r="I18" s="3">
-        <v>172500</v>
+        <v>173800</v>
       </c>
       <c r="J18" s="3">
-        <v>144200</v>
+        <v>145600</v>
       </c>
       <c r="K18" s="3">
         <v>177600</v>
@@ -1822,25 +1822,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="G20" s="3">
-        <v>2500</v>
+        <v>-1800</v>
       </c>
       <c r="H20" s="3">
-        <v>3100</v>
+        <v>-1200</v>
       </c>
       <c r="I20" s="3">
-        <v>-1000</v>
+        <v>2700</v>
       </c>
       <c r="J20" s="3">
-        <v>-2600</v>
+        <v>4600</v>
       </c>
       <c r="K20" s="3">
         <v>5600</v>
@@ -1923,25 +1923,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>201600</v>
+        <v>200600</v>
       </c>
       <c r="E21" s="3">
-        <v>202100</v>
+        <v>200600</v>
       </c>
       <c r="F21" s="3">
-        <v>193700</v>
+        <v>192600</v>
       </c>
       <c r="G21" s="3">
-        <v>218800</v>
+        <v>217800</v>
       </c>
       <c r="H21" s="3">
-        <v>201200</v>
+        <v>200600</v>
       </c>
       <c r="I21" s="3">
-        <v>198600</v>
+        <v>198200</v>
       </c>
       <c r="J21" s="3">
-        <v>168000</v>
+        <v>167500</v>
       </c>
       <c r="K21" s="3">
         <v>207900</v>
@@ -3034,25 +3034,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
-        <v>-800</v>
+        <v>-1800</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>-1400</v>
       </c>
       <c r="G32" s="3">
-        <v>-2500</v>
+        <v>1800</v>
       </c>
       <c r="H32" s="3">
-        <v>-3100</v>
+        <v>1200</v>
       </c>
       <c r="I32" s="3">
-        <v>1000</v>
+        <v>-2700</v>
       </c>
       <c r="J32" s="3">
-        <v>2600</v>
+        <v>-4600</v>
       </c>
       <c r="K32" s="3">
         <v>-5600</v>
@@ -3826,13 +3826,13 @@
         <v>530300</v>
       </c>
       <c r="F43" s="3">
-        <v>537700</v>
+        <v>533800</v>
       </c>
       <c r="G43" s="3">
-        <v>590900</v>
+        <v>590200</v>
       </c>
       <c r="H43" s="3">
-        <v>533800</v>
+        <v>524200</v>
       </c>
       <c r="I43" s="3">
         <v>527900</v>
@@ -4022,25 +4022,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>82100</v>
+        <v>5600</v>
       </c>
       <c r="E45" s="3">
-        <v>86300</v>
+        <v>7700</v>
       </c>
       <c r="F45" s="3">
-        <v>83000</v>
+        <v>12300</v>
       </c>
       <c r="G45" s="3">
-        <v>68000</v>
+        <v>700</v>
       </c>
       <c r="H45" s="3">
-        <v>60200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>58300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>62000</v>
+        <v>12600</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>48800</v>
@@ -4223,26 +4223,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4729,25 +4729,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>67600</v>
+        <v>47200</v>
       </c>
       <c r="E52" s="3">
-        <v>68600</v>
+        <v>48800</v>
       </c>
       <c r="F52" s="3">
-        <v>67600</v>
+        <v>48400</v>
       </c>
       <c r="G52" s="3">
-        <v>66500</v>
+        <v>50500</v>
       </c>
       <c r="H52" s="3">
-        <v>103500</v>
+        <v>91300</v>
       </c>
       <c r="I52" s="3">
-        <v>100800</v>
+        <v>88700</v>
       </c>
       <c r="J52" s="3">
-        <v>101200</v>
+        <v>89200</v>
       </c>
       <c r="K52" s="3">
         <v>97600</v>
@@ -5207,25 +5207,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>101600</v>
+        <v>118700</v>
       </c>
       <c r="E58" s="3">
-        <v>124600</v>
+        <v>141000</v>
       </c>
       <c r="F58" s="3">
-        <v>121600</v>
+        <v>138500</v>
       </c>
       <c r="G58" s="3">
-        <v>120600</v>
+        <v>137400</v>
       </c>
       <c r="H58" s="3">
-        <v>115200</v>
+        <v>132000</v>
       </c>
       <c r="I58" s="3">
-        <v>608000</v>
+        <v>625000</v>
       </c>
       <c r="J58" s="3">
-        <v>425800</v>
+        <v>443200</v>
       </c>
       <c r="K58" s="3">
         <v>397400</v>
@@ -5308,25 +5308,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>318400</v>
+        <v>118000</v>
       </c>
       <c r="E59" s="3">
-        <v>308200</v>
+        <v>131900</v>
       </c>
       <c r="F59" s="3">
-        <v>326900</v>
+        <v>144800</v>
       </c>
       <c r="G59" s="3">
-        <v>355200</v>
+        <v>163600</v>
       </c>
       <c r="H59" s="3">
-        <v>308400</v>
+        <v>140400</v>
       </c>
       <c r="I59" s="3">
-        <v>297000</v>
+        <v>136700</v>
       </c>
       <c r="J59" s="3">
-        <v>309000</v>
+        <v>148400</v>
       </c>
       <c r="K59" s="3">
         <v>337500</v>
@@ -5510,25 +5510,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1410600</v>
+        <v>1494400</v>
       </c>
       <c r="E61" s="3">
-        <v>1426700</v>
+        <v>1511500</v>
       </c>
       <c r="F61" s="3">
-        <v>1525700</v>
+        <v>1617400</v>
       </c>
       <c r="G61" s="3">
-        <v>1633100</v>
+        <v>1725500</v>
       </c>
       <c r="H61" s="3">
-        <v>738000</v>
+        <v>829200</v>
       </c>
       <c r="I61" s="3">
-        <v>356600</v>
+        <v>450100</v>
       </c>
       <c r="J61" s="3">
-        <v>606200</v>
+        <v>703400</v>
       </c>
       <c r="K61" s="3">
         <v>356500</v>
@@ -5611,25 +5611,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>421700</v>
+        <v>39000</v>
       </c>
       <c r="E62" s="3">
-        <v>420900</v>
+        <v>36600</v>
       </c>
       <c r="F62" s="3">
-        <v>445700</v>
+        <v>54800</v>
       </c>
       <c r="G62" s="3">
-        <v>438600</v>
+        <v>44200</v>
       </c>
       <c r="H62" s="3">
-        <v>350700</v>
+        <v>35300</v>
       </c>
       <c r="I62" s="3">
-        <v>349200</v>
+        <v>32200</v>
       </c>
       <c r="J62" s="3">
-        <v>359000</v>
+        <v>38600</v>
       </c>
       <c r="K62" s="3">
         <v>335300</v>
@@ -7407,25 +7407,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>33400</v>
+        <v>13200</v>
       </c>
       <c r="E83" s="3">
-        <v>32700</v>
+        <v>13100</v>
       </c>
       <c r="F83" s="3">
-        <v>33500</v>
+        <v>12600</v>
       </c>
       <c r="G83" s="3">
-        <v>31300</v>
+        <v>12200</v>
       </c>
       <c r="H83" s="3">
-        <v>27100</v>
+        <v>12200</v>
       </c>
       <c r="I83" s="3">
-        <v>27100</v>
+        <v>12400</v>
       </c>
       <c r="J83" s="3">
-        <v>26400</v>
+        <v>12300</v>
       </c>
       <c r="K83" s="3">
         <v>24700</v>
@@ -8592,25 +8592,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-39000</v>
+        <v>39000</v>
       </c>
       <c r="E96" s="3">
-        <v>-38900</v>
+        <v>38900</v>
       </c>
       <c r="F96" s="3">
-        <v>-38900</v>
+        <v>38900</v>
       </c>
       <c r="G96" s="3">
-        <v>-38800</v>
+        <v>38800</v>
       </c>
       <c r="H96" s="3">
-        <v>-37100</v>
+        <v>37100</v>
       </c>
       <c r="I96" s="3">
-        <v>-37300</v>
+        <v>37300</v>
       </c>
       <c r="J96" s="3">
-        <v>-37200</v>
+        <v>37200</v>
       </c>
       <c r="K96" s="3">
         <v>-37200</v>
@@ -9100,22 +9100,22 @@
         <v>-400</v>
       </c>
       <c r="E101" s="3">
-        <v>1400</v>
+        <v>-600</v>
       </c>
       <c r="F101" s="3">
-        <v>-5600</v>
+        <v>6600</v>
       </c>
       <c r="G101" s="3">
-        <v>-8400</v>
+        <v>-4900</v>
       </c>
       <c r="H101" s="3">
-        <v>-400</v>
+        <v>-1700</v>
       </c>
       <c r="I101" s="3">
-        <v>-600</v>
+        <v>-2800</v>
       </c>
       <c r="J101" s="3">
-        <v>6600</v>
+        <v>-1500</v>
       </c>
       <c r="K101" s="3">
         <v>-4900</v>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,454 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>615400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>744500</v>
+      </c>
+      <c r="F8" s="3">
         <v>661600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>650600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>633200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>719300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>648700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>650200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>610500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>683600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>662100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>635400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>609200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>599200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>646900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>589500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>526600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>558500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>538200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>529500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>494900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>585500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>559700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>551100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>497900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>569300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>581200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>553700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>550400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>573900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>589400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>496100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>407500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>279500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>341700</v>
+      </c>
+      <c r="F9" s="3">
         <v>292600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>284800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>284800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>335200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>288400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>298000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>281600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>320400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>296500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>277800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>269000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>268100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>281600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>251800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>236600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>261700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>257400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>239900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>231700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>266500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>257100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>249600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>228900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>261400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>260800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>246700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>249500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>261900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>263200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>220600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>182300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>402800</v>
+      </c>
+      <c r="F10" s="3">
         <v>369000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>365900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>348400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>384100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>360300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>352100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>328900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>363200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>365600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>357600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>340200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>331100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>365300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>337700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>290000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>296800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>280800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>289600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>263200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>319000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>302600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>301500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>269000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>307900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>320400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>307000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>300900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>312000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>326200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>275500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>225200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,28 +1165,30 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>65000</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>71400</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>71400</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1375,14 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1367,38 +1407,38 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>87400</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>87400</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1406,74 +1446,80 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>1500</v>
-      </c>
       <c r="AA14" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>1500</v>
       </c>
       <c r="AC14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>1100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F15" s="3">
         <v>33400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>32700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>33500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>31300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>27100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>27100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>26400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>473500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>562300</v>
+      </c>
+      <c r="F17" s="3">
         <v>493600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>481000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>472700</v>
       </c>
-      <c r="G17" s="3">
-        <v>534600</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>529600</v>
+      </c>
+      <c r="J17" s="3">
         <v>476300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>476300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>464900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>506000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>477200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>451400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>453300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>447800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>458600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>423100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>417500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>521200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>426100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>404400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>419800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>445800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>429500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>422200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>413600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>452500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>443700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>422300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>431100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>449200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>436000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>392600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>331600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>182200</v>
+      </c>
+      <c r="F18" s="3">
         <v>168000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>169600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>160500</v>
       </c>
-      <c r="G18" s="3">
-        <v>184700</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>189700</v>
+      </c>
+      <c r="J18" s="3">
         <v>172300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>173800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>145600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>177600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>184900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>184000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>155900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>151400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>188300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>166400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>109100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>37300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>112100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>125100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>75100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>139700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>130200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>128900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>84300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>116800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>137500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>131400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>119300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>124800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>153400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>103500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>75900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1882,545 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>4600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>5600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-39300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-4200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-9300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-3900</v>
       </c>
       <c r="AA20" s="3">
         <v>-200</v>
       </c>
       <c r="AB20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>211900</v>
+      </c>
+      <c r="F21" s="3">
         <v>200600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>200600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>192600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>217800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>200600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>198200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>167500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>207900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>211100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>169600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>183000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>171000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>213400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>188300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>130800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>62300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>131300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>151900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>101500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>165100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>158800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>156400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>108200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>143900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>163800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>157700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>141100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>150100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>179700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>123400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>94500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F22" s="3">
         <v>18800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>20100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>21400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>27000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>9900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>10500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>5700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>5400</v>
       </c>
       <c r="N22" s="3">
         <v>5700</v>
       </c>
       <c r="O22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>7100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>6800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>7300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>8300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>9700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>10900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>11500</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>12400</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>12400</v>
       </c>
       <c r="AA22" s="3">
         <v>12400</v>
       </c>
       <c r="AB22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AD22" s="3">
         <v>13800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>12100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>11300</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>11700</v>
       </c>
       <c r="AF22" s="3">
         <v>11300</v>
       </c>
       <c r="AG22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AI22" s="3">
         <v>7900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>5600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>148100</v>
+      </c>
+      <c r="F23" s="3">
         <v>149400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>149300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>138700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>160600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>162100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>161600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>131100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>177500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>180500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>139300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>152000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>140100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>180400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>155900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>97800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>26300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>95500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>116600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>63100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>127300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>119500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>116300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>68000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>104200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>122700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>118100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>103500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>112900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>142500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>94600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>70400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F24" s="3">
         <v>32100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>31100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>29100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>32800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>34200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>34100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>26800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>36300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>38700</v>
-      </c>
-      <c r="M24" s="3">
-        <v>29600</v>
-      </c>
-      <c r="N24" s="3">
-        <v>31600</v>
       </c>
       <c r="O24" s="3">
         <v>29600</v>
       </c>
       <c r="P24" s="3">
+        <v>31600</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>29600</v>
+      </c>
+      <c r="R24" s="3">
         <v>38200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>31700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>20200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>8500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>24500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>11100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>24600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>25600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>24400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>14600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>16900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>27800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>26900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>33000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>41000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>30100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>20400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F26" s="3">
         <v>117300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>118200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>109600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>127800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>127900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>127600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>104300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>141200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>141800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>109600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>120400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>110500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>142200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>124100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>77600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>18500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>87000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>92100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>52000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>102700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>93900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>91900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>53400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>87300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>94900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>91200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>104600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>79800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>101500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>64500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>50000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F27" s="3">
         <v>117300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>118200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>109600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>127800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>127900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>127600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>104300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>141200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>141800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>109600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>120400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>110500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>142200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>124100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>77600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>18500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>87000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>92100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>52000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>102700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>93900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>91900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>53400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>87300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>94900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>91200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>104600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>79800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>101500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>64500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>50000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2778,44 +2900,44 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-600</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>22100</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3162,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O32" s="3">
+        <v>39300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>39300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>4200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>9300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>3900</v>
       </c>
       <c r="AA32" s="3">
         <v>200</v>
       </c>
       <c r="AB32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>4500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F33" s="3">
         <v>117300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>118200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>109600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>127800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>127900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>127600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>104300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>141200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>141800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>109600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>120400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>110500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>142200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>124100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>77600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>18500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>87000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>92100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>52000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>102700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>93900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>91900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>48600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>86700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>94900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>91200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>126600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>79800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>101500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>64500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>50000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F35" s="3">
         <v>117300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>118200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>109600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>127800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>127900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>127600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>104300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>141200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>141800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>109600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>120400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>110500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>142200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>124100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>77600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>18500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>87000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>92100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>52000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>102700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>93900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>91900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>48600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>86700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>94900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>91200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>126600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>79800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>101500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>64500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>50000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3784,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>116000</v>
+      </c>
+      <c r="F41" s="3">
         <v>165300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>125400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>136200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>115700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>143100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>129100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>122000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>163500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>128700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>120900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>170500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>300000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>174200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>133300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>225700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>208300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>221800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>306300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>115100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>151200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>147800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>149200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>85500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>95700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>266800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>155900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>132800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>90400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>110700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>88400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>87700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,412 +3994,442 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>531300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>594700</v>
+      </c>
+      <c r="F43" s="3">
         <v>538500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>530300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>533800</v>
       </c>
-      <c r="G43" s="3">
-        <v>590200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>590900</v>
+      </c>
+      <c r="J43" s="3">
         <v>524200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>527900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>546600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>537300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>530800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>499500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>465700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>489400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>516700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>470600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>455400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>471900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>498300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>474900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>471600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>530800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>500000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>489700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>463200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>491400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>507700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>512400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>488300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>505100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>498800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>428700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>358400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>472200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>476900</v>
+      </c>
+      <c r="F44" s="3">
         <v>438200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>443600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>451200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>454800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>439700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>440200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>447700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>383400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>399600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>383200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>366400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>327200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>304000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>295800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>282400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>277000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>310600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>312100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>294800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>283400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>282600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>280700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>271200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>264500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>271400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>284400</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>275700</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>264300</v>
       </c>
       <c r="AF44" s="3">
         <v>275700</v>
       </c>
       <c r="AG44" s="3">
+        <v>264300</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>275700</v>
+      </c>
+      <c r="AI44" s="3">
         <v>275800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>241300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>12300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12600</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>48800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>56500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>56200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>51600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>48300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>50900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>49600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>64600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>63400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>50100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>50000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>48800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>45900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>50300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>45300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>47300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>32500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>32000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>31300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>31200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>28600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>34900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>35900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>32700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1275000</v>
+      </c>
+      <c r="F46" s="3">
         <v>1224100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1185600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1208100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1229300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1176900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1155400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1178400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1133000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1115600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1059800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1054200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1164800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1045800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>949400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1028100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1020600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1080700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1143300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>930300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1011200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>980700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>964900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>867200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>884100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1077800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>984000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>928000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>888400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>920200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>828800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>720000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,11 +4454,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4319,210 +4529,228 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>626300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>638200</v>
+      </c>
+      <c r="F48" s="3">
         <v>498000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>492400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>499800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>499000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>455300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>462000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>472800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>455700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>459700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>463500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>473300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>466400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>473800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>482300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>481700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>480700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>547000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>526200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>530700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>398900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>392000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>386300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>387700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>386700</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>356800</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>359500</v>
       </c>
       <c r="AD48" s="3">
         <v>356800</v>
       </c>
       <c r="AE48" s="3">
+        <v>359500</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>356800</v>
+      </c>
+      <c r="AG48" s="3">
         <v>346400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>335700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>320000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>269800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3946800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4021700</v>
+      </c>
+      <c r="F49" s="3">
         <v>3414500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3425300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3471600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3456900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2461300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2474900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2484900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2134100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2157000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2179000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2210600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2070500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2089300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2104800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2119800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2120900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2137700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2028200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2045400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2060300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2072500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2078700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2097700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2107800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2126600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2148300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>54800</v>
+      </c>
+      <c r="F52" s="3">
         <v>47200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>48800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>48400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>50500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>91300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>88700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>89200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>97600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>91500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>93900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>96800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>89200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>61200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>58300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>53800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>52400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>54500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>45200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>44500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>46000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>46300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>45100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>45100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>42500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>46200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>47400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>45700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>43400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>57200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>55900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>34900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5871500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6001000</v>
+      </c>
+      <c r="F54" s="3">
         <v>5204400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5171900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5247100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5251800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4197000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4193100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4237400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3820400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3823800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3796300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3835000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3791000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3670100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3594900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3683400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3674700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3820000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3742900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3550900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3516400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3491500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3475100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3397700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3421000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3607400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3539200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5360,652 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>97800</v>
+      </c>
+      <c r="F57" s="3">
         <v>98300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>103200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>103200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>106300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>105100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>85400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>90600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>99300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>100400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>96900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>96500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>91700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>92900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>84800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>74100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>70900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>71400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>79800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>78100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>85100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>85600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>93000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>81000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>83600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>80800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>86800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>82100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>86000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>80700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>85200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>74000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>126300</v>
+      </c>
+      <c r="F58" s="3">
         <v>118700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>141000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>138500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>137400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>132000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>625000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>443200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>397400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>407000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>316200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>39900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>40000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>37200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>44100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>44100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>44000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>49800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>49800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>49300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>174100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>173500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>158400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>58400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>33300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>38600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>231500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>331700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>331400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>132200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>145500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>46600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>108900</v>
+      </c>
+      <c r="F59" s="3">
         <v>118000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>131900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>144800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>163600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>140400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>136700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>148400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>337500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>319900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>309400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>293100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>313700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>290700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>256300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>241300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>248100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>226000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>230600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>216000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>218400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>185200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>195100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>185100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>233400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>221700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>216400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>196000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>230300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>224400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>225800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>169600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>484100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>528500</v>
+      </c>
+      <c r="F60" s="3">
         <v>518300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>536000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>551700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>582100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>528600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>990400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>825500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>834200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>827300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>722500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>429500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>445400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>420800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>385300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>359600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>363100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>347200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>360200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>343300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>477600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>444200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>446500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>324500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>350300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>341100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>534700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>609800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>647700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>437400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>456500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>290200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2172300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2194100</v>
+      </c>
+      <c r="F61" s="3">
         <v>1494400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1511500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1617400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1725500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>829200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>450100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>703400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>356500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>415200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>493200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>787900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>796700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>804800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>845000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>992100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1078400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1232100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1248300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1084400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1084900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1179900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1220400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1331400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1294200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1521400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1312500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>912400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>42100</v>
+      </c>
+      <c r="F62" s="3">
         <v>39000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>36600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>54800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>44200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>35300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>32200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>38600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>335300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>382300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>390100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>399000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>389800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>381300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>414300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>474500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>474200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>470800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>481900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>488900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>372900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>320600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>336900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>340300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>325800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>322000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>329200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>336900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>345200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>369000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>386300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>296600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2994900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3068800</v>
+      </c>
+      <c r="F66" s="3">
         <v>2350600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2383600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2523100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2653700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1617200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1696100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1790700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1526000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1624800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1605700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1616400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1631800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1606900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1644600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1826200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1915700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2050000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2090400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1916600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1935400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1944700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2003800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1996200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1970300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2184500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2176300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4345200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4295200</v>
+      </c>
+      <c r="F72" s="3">
         <v>4217700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4139300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4060100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3989400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3900400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3809600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3719300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3652200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3548200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3435800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3355700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3265000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3184200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3064700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2963300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2908700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2912800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2847800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2776700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2747700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2666800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2593000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2521100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2488400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2403200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2325700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2876600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2932200</v>
+      </c>
+      <c r="F76" s="3">
         <v>2853800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2788300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2724000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2598100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2579800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2497000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2446700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2294400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2199000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2190600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2218600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2159100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2063200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1950400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1857200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1759000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1769900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1652500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1634300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1581000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1546900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1471300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1401500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1450700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1422900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1362900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>962300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>893800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F81" s="3">
         <v>117300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>118200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>109600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>127800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>127900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>127600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>104300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>141200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>141800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>109600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>120400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>110500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>142200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>124100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>77600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>18500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>87000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>92100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>52000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>102700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>93900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>91900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>48600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>86700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>94900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>91200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>126600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>79800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>101500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>64500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>50000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7797,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F83" s="3">
         <v>13200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>13100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>12600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>12200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>12200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>12400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>12300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>24700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>24900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>25400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>25700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>26900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>25300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>26000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>29100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>28500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>27000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>28600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>26900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>27800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>27700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>27700</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>27400</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>27300</v>
       </c>
       <c r="AC83" s="3">
         <v>27400</v>
       </c>
       <c r="AD83" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>27400</v>
+      </c>
+      <c r="AF83" s="3">
         <v>26300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>25500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>26000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>20900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>18500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>96400</v>
+      </c>
+      <c r="F89" s="3">
         <v>164800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>122600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>172400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>163200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>190200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>164600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>123300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>173400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>125200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>96400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>118100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>170500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>127700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>104400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>143300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>192500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>91800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>101900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>116300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>146500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>74500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>105100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>56800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>161700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>130600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>103000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>109300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>135000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>82400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>58200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>81200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8585,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-14400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-7500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-10300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-8900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-9300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-12100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-14600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-12300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-10200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-10800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-7900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-14400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-10300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-12000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-13900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-18200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8902,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-809500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-19700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-9500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1034900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-387100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-12200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-14200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-12300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-184100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-5800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-7900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-30900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-135500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-13900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-13800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-18400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-32200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-48900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +9052,117 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>44600</v>
+      </c>
+      <c r="F96" s="3">
         <v>39000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>38900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>38900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>38800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>37100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>37300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>37200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-37200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-29400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-29600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-29700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-29700</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-22700</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-22700</v>
       </c>
       <c r="R96" s="3">
         <v>-22700</v>
       </c>
       <c r="S96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="T96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="U96" s="3">
         <v>-22600</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-21900</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-22000</v>
       </c>
       <c r="V96" s="3">
         <v>-21900</v>
       </c>
       <c r="W96" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-21800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9476,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-127600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>665100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-104900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-125300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-140500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>852600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-166900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-150900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>215700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-121600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-101500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-131000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-61900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-34800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-77800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-188100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-122300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-176100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-44400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>107200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-138200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-121500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-43000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-31300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-280200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>749100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>4300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>3600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-4100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-3300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>2200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>4900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>3200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="F102" s="3">
         <v>39900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-10800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>20500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-27500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>14100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-41500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>34700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>7800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-49600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-129400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>125700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>40900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-92400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>17400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-13500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-84500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>191200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-36100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>63600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-171100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>110900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>23100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>42500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>22300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>20400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,480 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45869</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="F7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>682900</v>
+      </c>
+      <c r="F8" s="3">
         <v>615400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>744500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>661600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>650600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>633200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>719300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>648700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>650200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>610500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>683600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>662100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>635400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>609200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>599200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>646900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>589500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>526600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>558500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>538200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>529500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>494900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>585500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>559700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>551100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>497900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>569300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>581200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>553700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>550400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>573900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>589400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>496100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>407500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>309000</v>
+      </c>
+      <c r="F9" s="3">
         <v>279500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>341700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>292600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>284800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>284800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>335200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>288400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>298000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>281600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>320400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>296500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>277800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>269000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>268100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>281600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>251800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>236600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>261700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>257400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>239900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>231700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>266500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>257100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>249600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>228900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>261400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>260800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>246700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>249500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>261900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>263200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>220600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>182300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>373900</v>
+      </c>
+      <c r="F10" s="3">
         <v>335900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>402800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>369000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>365900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>348400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>384100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>360300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>352100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>328900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>363200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>365600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>357600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>340200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>331100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>365300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>337700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>290000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>296800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>280800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>289600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>263200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>319000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>302600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>301500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>269000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>307900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>320400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>307000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>300900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>312000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>326200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>275500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>225200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,35 +1192,37 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>65000</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>71400</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1301,14 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1414,14 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1413,119 +1452,125 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>87400</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>1500</v>
-      </c>
       <c r="AC14" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="3">
         <v>1500</v>
       </c>
       <c r="AE14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>1100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>37600</v>
+      </c>
+      <c r="F15" s="3">
         <v>37000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>36500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>33400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>32700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>33500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>31300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>27100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>27100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>26400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1640,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1682,236 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
+        <v>513200</v>
+      </c>
+      <c r="F17" s="3">
         <v>473500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>562300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>493600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>481000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>472700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>529600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>476300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>476300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>464900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>506000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>477200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>451400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>453300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>447800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>458600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>423100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>417500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>521200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>426100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>404400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>419800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>445800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>429500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>422200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>413600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>452500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>443700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>422300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>431100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>449200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>436000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>392600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>331600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
+        <v>169800</v>
+      </c>
+      <c r="F18" s="3">
         <v>142000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>182200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>168000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>169600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>160500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>189700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>172300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>173800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>145600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>177600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>184900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>184000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>155900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>151400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>188300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>166400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>109100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>37300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>112100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>125100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>75100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>139700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>130200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>128900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>84300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>116800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>137500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>131400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>119300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>124800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>153400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>103500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>75900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,543 +1949,575 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>3200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>5600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-39300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-4300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-4200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-9300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-3900</v>
       </c>
       <c r="AC20" s="3">
         <v>-200</v>
       </c>
       <c r="AD20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>202400</v>
+      </c>
+      <c r="F21" s="3">
         <v>179500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>211900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>200600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>200600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>192600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>217800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>200600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>198200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>167500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>207900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>211100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>169600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>183000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>171000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>213400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>188300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>130800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>62300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>131300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>151900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>101500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>165100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>158800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>156400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>108200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>143900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>163800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>157700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>141100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>150100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>179700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>123400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>94500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>26600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>26600</v>
+      </c>
+      <c r="G22" s="3">
         <v>28600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>18800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>20100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>21400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>27000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>12100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>9900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>10500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
-      </c>
-      <c r="N22" s="3">
-        <v>5700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>5400</v>
       </c>
       <c r="P22" s="3">
         <v>5700</v>
       </c>
       <c r="Q22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="R22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="S22" s="3">
         <v>5300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>6900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>6800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>8300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>9700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>10900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>11500</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>12400</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>12400</v>
       </c>
       <c r="AC22" s="3">
         <v>12400</v>
       </c>
       <c r="AD22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AF22" s="3">
         <v>13800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>12100</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>11300</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>11700</v>
       </c>
       <c r="AH22" s="3">
         <v>11300</v>
       </c>
       <c r="AI22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AK22" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>5600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
+        <v>138800</v>
+      </c>
+      <c r="F23" s="3">
         <v>116900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>148100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>149400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>149300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>138700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>160600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>162100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>161600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>131100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>177500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>180500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>139300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>152000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>140100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>180400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>155900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>97800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>26300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>95500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>116600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>63100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>127300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>119500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>116300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>68000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>104200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>122700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>118100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>103500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>112900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>142500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>94600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>70400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F24" s="3">
         <v>22200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>25900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>32100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>31100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>29100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>32800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>34200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>34100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>26800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>36300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>38700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>29600</v>
-      </c>
-      <c r="P24" s="3">
-        <v>31600</v>
       </c>
       <c r="Q24" s="3">
         <v>29600</v>
       </c>
       <c r="R24" s="3">
+        <v>31600</v>
+      </c>
+      <c r="S24" s="3">
+        <v>29600</v>
+      </c>
+      <c r="T24" s="3">
         <v>38200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>31700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>20200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>7800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>8500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>24500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>11100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>24600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>25600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>24400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>14600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>16900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>27800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>26900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>33000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>41000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>20400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2623,240 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
+        <v>112400</v>
+      </c>
+      <c r="F26" s="3">
         <v>94700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>122200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>117300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>118200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>109600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>127800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>127900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>127600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>104300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>141200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>141800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>109600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>120400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>110500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>142200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>124100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>77600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>18500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>87000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>92100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>52000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>102700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>93900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>91900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>53400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>87300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>94900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>91200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>104600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>79800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>101500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>50000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>112400</v>
+      </c>
+      <c r="F27" s="3">
         <v>94700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>122200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>117300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>118200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>109600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>127800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>127900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>127600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>104300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>141200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>141800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>109600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>120400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>110500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>142200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>124100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>77600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>18500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>87000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>92100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>52000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>102700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>93900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>91900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>53400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>87300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>94900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>91200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>104600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>79800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>101500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>50000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2906,45 +3027,45 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>-600</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>22100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2954,8 +3075,14 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3301,240 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-3200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-5600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>39300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>4300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>4200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>9300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>3900</v>
       </c>
       <c r="AC32" s="3">
         <v>200</v>
       </c>
       <c r="AD32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>4500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>112400</v>
+      </c>
+      <c r="F33" s="3">
         <v>94700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>122200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>117300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>118200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>109600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>127800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>127900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>127600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>104300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>141200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>141800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>109600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>120400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>110500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>142200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>124100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>77600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>18500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>87000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>92100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>52000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>102700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>93900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>91900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>48600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>86700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>94900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>91200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>126600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>79800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>101500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>50000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3640,245 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
+        <v>112400</v>
+      </c>
+      <c r="F35" s="3">
         <v>94700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>122200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>117300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>118200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>109600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>127800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>127900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>127600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>104300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>141200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>141800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>109600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>120400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>110500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>142200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>124100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>77600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>18500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>87000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>92100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>52000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>102700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>93900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>91900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>48600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>86700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>94900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>91200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>126600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>79800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>101500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>50000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45869</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="F38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3957,123 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
+        <v>130200</v>
+      </c>
+      <c r="F41" s="3">
         <v>130400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>116000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>165300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>125400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>136200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>115700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>143100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>129100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>122000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>163500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>128700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>120900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>170500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>300000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>174200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>133300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>225700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>208300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>221800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>306300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>115100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>151200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>147800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>149200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>85500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>95700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>266800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>155900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>132800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>90400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>110700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>88400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>87700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,436 +4179,466 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>624100</v>
+      </c>
+      <c r="F43" s="3">
         <v>531300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>594700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>538500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>530300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>533800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>590900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>524200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>527900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>546600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>537300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>530800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>499500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>465700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>489400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>516700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>470600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>455400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>471900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>498300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>474900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>471600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>530800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>500000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>489700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>463200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>491400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>507700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>512400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>488300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>505100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>498800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>428700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>358400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
+        <v>473700</v>
+      </c>
+      <c r="F44" s="3">
         <v>472200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>476900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>438200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>443600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>451200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>454800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>439700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>440200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>447700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>383400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>399600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>383200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>366400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>327200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>304000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>295800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>282400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>277000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>310600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>312100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>294800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>283400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>282600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>280700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>271200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>264500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>271400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>284400</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>275700</v>
-      </c>
-      <c r="AG44" s="3">
-        <v>264300</v>
       </c>
       <c r="AH44" s="3">
         <v>275700</v>
       </c>
       <c r="AI44" s="3">
+        <v>264300</v>
+      </c>
+      <c r="AJ44" s="3">
+        <v>275700</v>
+      </c>
+      <c r="AK44" s="3">
         <v>275800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>241300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F45" s="3">
         <v>14500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>7700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>12600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>48800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>56500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>56200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>51600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>48300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>50900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>49600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>64600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>63400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>50100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>50000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>48800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>45900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>50300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>45300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>47300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>32500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>32000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>31300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>31200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>28600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>34900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>35900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>32700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1323500</v>
+      </c>
+      <c r="F46" s="3">
         <v>1226000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1275000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1224100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1185600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1208100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1229300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1176900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1155400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1178400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1133000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1115600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1059800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1054200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1164800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1045800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>949400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1028100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1020600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1080700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1143300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>930300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1011200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>980700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>964900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>867200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>884100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1077800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>984000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>928000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>888400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>920200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>828800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>720000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4460,11 +4669,11 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4535,222 +4744,240 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
+        <v>633900</v>
+      </c>
+      <c r="F48" s="3">
         <v>626300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>638200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>498000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>492400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>499800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>499000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>455300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>462000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>472800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>455700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>459700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>463500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>473300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>466400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>473800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>482300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>481700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>480700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>547000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>526200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>530700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>398900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>392000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>386300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>387700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>386700</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>356800</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>359500</v>
       </c>
       <c r="AF48" s="3">
         <v>356800</v>
       </c>
       <c r="AG48" s="3">
+        <v>359500</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>356800</v>
+      </c>
+      <c r="AI48" s="3">
         <v>346400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>335700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>320000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>269800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4026100</v>
+      </c>
+      <c r="F49" s="3">
         <v>3946800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4021700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3414500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3425300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3471600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3456900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2461300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2474900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2484900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2134100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2157000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2179000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2210600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2070500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2089300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2104800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2119800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2120900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2137700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2028200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2045400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2060300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2072500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2078700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2097700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2107800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>2126600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>2148300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5196,127 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
+        <v>64500</v>
+      </c>
+      <c r="F52" s="3">
         <v>60700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>54800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>47200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>48800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>48400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>50500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>91300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>88700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>89200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>97600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>91500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>93900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>96800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>89200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>61200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>58300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>53800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>52400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>54500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>45200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>44500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>46000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>46300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>45100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>45100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>42500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>46200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>47400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>45700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>43400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>57200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>34900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5422,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6062000</v>
+      </c>
+      <c r="F54" s="3">
         <v>5871500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6001000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5204400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5171900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5247100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5251800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4197000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4193100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4237400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3820400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3823800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3796300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3835000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3791000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3670100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3594900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3683400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3674700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3820000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3742900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3550900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3516400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3491500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3475100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3397700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3421000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3607400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3539200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5621,688 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
+        <v>119900</v>
+      </c>
+      <c r="F57" s="3">
         <v>88500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>97800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>98300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>103200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>103200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>106300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>105100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>85400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>90600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>99300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>100400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>96900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>96500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>91700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>92900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>84800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>74100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>70900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>71400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>79800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>78100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>85100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>85600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>93000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>81000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>83600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>80800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>86800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>82100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>86000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>80700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>85200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>74000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
+        <v>118000</v>
+      </c>
+      <c r="F58" s="3">
         <v>122900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>126300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>118700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>141000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>138500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>137400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>132000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>625000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>443200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>397400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>407000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>316200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>39900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>40000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>37200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>44100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>44100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>44000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>49800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>49800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>49300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>174100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>173500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>158400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>58400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>33300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>38600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>231500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>331700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>331400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>132200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>145500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>46600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
+        <v>92800</v>
+      </c>
+      <c r="F59" s="3">
         <v>102500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>108900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>118000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>131900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>144800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>163600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>140400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>136700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>148400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>337500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>319900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>309400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>293100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>313700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>290700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>256300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>241300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>248100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>226000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>230600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>216000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>218400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>185200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>195100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>185100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>233400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>221700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>216400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>196000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>230300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>224400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>225800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>169600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
+        <v>516600</v>
+      </c>
+      <c r="F60" s="3">
         <v>484100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>528500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>518300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>536000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>551700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>582100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>528600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>990400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>825500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>834200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>827300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>722500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>429500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>445400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>420800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>385300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>359600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>363100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>347200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>360200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>343300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>477600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>444200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>446500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>324500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>350300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>341100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>534700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>609800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>647700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>437400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>456500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>290200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2205500</v>
+      </c>
+      <c r="F61" s="3">
         <v>2172300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2194100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1494400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1511500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1617400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1725500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>829200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>450100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>703400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>356500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>415200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>493200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>787900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>796700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>804800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>845000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>992100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1078400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1232100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1248300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1084400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1084900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1179900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1220400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1331400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1294200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1521400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1312500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>912400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
+        <v>77200</v>
+      </c>
+      <c r="F62" s="3">
         <v>33800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>42100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>39000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>36600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>54800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>44200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>35300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>32200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>38600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>335300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>382300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>390100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>399000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>389800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>381300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>414300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>474500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>474200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>470800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>481900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>488900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>372900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>320600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>336900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>340300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>325800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>322000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>329200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>336900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>345200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>369000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>386300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>296600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6634,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3101700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2994900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3068800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2350600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2383600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2523100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2653700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1617200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1696100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1790700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1526000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1624800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1605700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1616400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1631800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1606900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1644600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1826200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1915700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2050000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2090400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1916600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1935400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1944700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2003800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1996200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1970300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2184500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2176300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +7127,14 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7240,127 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4413300</v>
+      </c>
+      <c r="F72" s="3">
         <v>4345200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4295200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4217700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4139300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4060100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3989400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3900400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3809600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3719300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3652200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3548200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3435800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3355700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3265000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3184200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3064700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2963300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2908700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2912800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2847800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2776700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2747700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2666800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2593000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2521100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2488400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2403200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2325700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7692,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2960300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2876600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2932200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2853800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2788300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2724000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2598100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2579800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2497000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2446700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2294400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2199000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2190600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2218600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2159100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2063200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1950400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1857200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1759000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1769900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1652500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1634300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1581000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1546900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1471300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1401500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1450700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1422900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1362900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>962300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>893800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7918,245 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45869</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="F80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
+        <v>112400</v>
+      </c>
+      <c r="F81" s="3">
         <v>94700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>122200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>117300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>118200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>109600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>127800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>127900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>127600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>104300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>141200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>141800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>109600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>120400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>110500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>142200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>124100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>77600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>18500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>87000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>92100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>52000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>102700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>93900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>91900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>48600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>86700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>94900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>91200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>126600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>79800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>101500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>50000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +8194,123 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F83" s="3">
         <v>14200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>13400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>13200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>13100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>12600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>12200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>12200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>12400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>12300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>24700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>24900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>25000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>25400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>25700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>26900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>25300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>26000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>29100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>28500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>27000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>28600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>26900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>27800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>27700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>27700</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>27400</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>27300</v>
       </c>
       <c r="AE83" s="3">
         <v>27400</v>
       </c>
       <c r="AF83" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>27400</v>
+      </c>
+      <c r="AH83" s="3">
         <v>26300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>25500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>26000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>18500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8868,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
+        <v>119200</v>
+      </c>
+      <c r="F89" s="3">
         <v>159100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>96400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>164800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>122600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>172400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>163200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>190200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>164600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>123300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>173400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>125200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>96400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>118100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>170500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>127700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>104400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>143300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>192500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>91800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>101900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>116300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>146500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>74500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>105100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>56800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>161700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>130600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>103000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>109300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>135000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>82400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>58200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>81200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +9026,123 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-20600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-21900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-14400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-10300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-6000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-12100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-14600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-12300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-10200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-9300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-10800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-7900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-14400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-10300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-12000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9361,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-14300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-809500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-19700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-9500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-5700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1034900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-387100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-12200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-14200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-12300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-184100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-10200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-9300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-5800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-7900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-30900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-135500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-13900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-18400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-32200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-48900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,115 +9519,123 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
+        <v>44300</v>
+      </c>
+      <c r="F96" s="3">
         <v>44600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>44600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>39000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>38900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>38900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>38800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>37100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>37300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>37200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-37200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-29400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-29600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-29700</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-22700</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-22700</v>
       </c>
       <c r="T96" s="3">
         <v>-22700</v>
       </c>
       <c r="U96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="V96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="W96" s="3">
         <v>-22600</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-21900</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-22000</v>
       </c>
       <c r="X96" s="3">
         <v>-21900</v>
       </c>
       <c r="Y96" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-21800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-20200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9967,349 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-113200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-127600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>665100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-104900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-125300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-140500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>852600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-166900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-150900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>215700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-121600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-101500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-131000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-61900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-34800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-77800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-188100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-122300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-176100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-44400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>107200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-138200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-121500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-43000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-31300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-280200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>749100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>6600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>4300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>3600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>4900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>3200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
         <v>14500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-49400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>39900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-10800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>20500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-27500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>14100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-41500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>34700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>7800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-49600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-129400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>125700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>40900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-92400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>17400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-13500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-84500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>191200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>63600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-171100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>110900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>23100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>42500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>22300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>20400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,505 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>669500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>751800</v>
+      </c>
+      <c r="F8" s="3">
         <v>741500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>682900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>615400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>744500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>661600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>650600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>633200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>719300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>648700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>650200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>610500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>683600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>662100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>635400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>609200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>599200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>646900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>589500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>526600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>558500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>538200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>529500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>494900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>585500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>559700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>551100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>497900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>569300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>581200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>553700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>550400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>573900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>589400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>496100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>407500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>325200</v>
+      </c>
+      <c r="F9" s="3">
         <v>335000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>309000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>279500</v>
       </c>
-      <c r="G9" s="3">
-        <v>341700</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>334000</v>
+      </c>
+      <c r="J9" s="3">
         <v>292600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>284800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>284800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>335200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>288400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>298000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>281600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>320400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>296500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>277800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>269000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>268100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>281600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>251800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>236600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>261700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>257400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>239900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>231700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>266500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>257100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>249600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>228900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>261400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>260800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>246700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>249500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>261900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>263200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>220600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>182300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>366100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>426600</v>
+      </c>
+      <c r="F10" s="3">
         <v>406500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>373900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>335900</v>
       </c>
-      <c r="G10" s="3">
-        <v>402800</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>410500</v>
+      </c>
+      <c r="J10" s="3">
         <v>369000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>365900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>348400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>384100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>360300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>352100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>328900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>363200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>365600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>357600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>340200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>331100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>365300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>337700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>290000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>296800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>280800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>289600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>263200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>319000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>302600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>301500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>269000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>307900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>320400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>307000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>300900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>312000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>326200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>275500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>225200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,40 +1220,42 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>68200</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>65000</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>65000</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
-        <v>71400</v>
+      <c r="K12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
+      <c r="M12" s="3">
+        <v>71400</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1307,8 +1335,14 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,19 +1454,25 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>12200</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1440,8 +1480,8 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>7700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1458,38 +1498,38 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>87400</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>87400</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1497,86 +1537,92 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>1500</v>
-      </c>
       <c r="AE14" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>1500</v>
       </c>
       <c r="AG14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>1100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>38100</v>
+      </c>
+      <c r="F15" s="3">
         <v>37800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>37600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>37000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>36500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>33400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>32700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>33500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>31300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>27100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>27100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>26400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1646,8 +1692,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1736,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>544700</v>
+        <v>502100</v>
       </c>
       <c r="E17" s="3">
+        <v>532600</v>
+      </c>
+      <c r="F17" s="3">
+        <v>540000</v>
+      </c>
+      <c r="G17" s="3">
         <v>513200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>473500</v>
       </c>
-      <c r="G17" s="3">
-        <v>562300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>556400</v>
+      </c>
+      <c r="J17" s="3">
         <v>493000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>481000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>472700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>529600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>476300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>476300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>464900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>506000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>477200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>451400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>453300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>447800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>458600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>423100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>417500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>521200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>426100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>404400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>419800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>445800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>429500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>422200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>413600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>452500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>443700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>422300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>431100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>449200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>436000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>392600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>331600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>196800</v>
+        <v>167300</v>
       </c>
       <c r="E18" s="3">
+        <v>219200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>201500</v>
+      </c>
+      <c r="G18" s="3">
         <v>169800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>142000</v>
       </c>
-      <c r="G18" s="3">
-        <v>182200</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>188100</v>
+      </c>
+      <c r="J18" s="3">
         <v>168600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>169600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>160500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>189700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>172300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>173800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>145600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>177600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>184900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>184000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>155900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>151400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>188300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>166400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>109100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>37300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>112100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>125100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>75100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>139700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>130200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>128900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>84300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>116800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>137500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>131400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>119300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>124800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>153400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>103500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>75900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,573 +2017,605 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F20" s="3">
         <v>4500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1400</v>
-      </c>
       <c r="I20" s="3">
-        <v>1800</v>
+        <v>5000</v>
       </c>
       <c r="J20" s="3">
         <v>1400</v>
       </c>
       <c r="K20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-39300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-4200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-3900</v>
       </c>
       <c r="AE20" s="3">
         <v>-200</v>
       </c>
       <c r="AF20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>230200</v>
+        <v>223800</v>
       </c>
       <c r="E21" s="3">
+        <v>248200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>234900</v>
+      </c>
+      <c r="G21" s="3">
         <v>202400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>179500</v>
       </c>
-      <c r="G21" s="3">
-        <v>211900</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>219600</v>
+      </c>
+      <c r="J21" s="3">
         <v>200600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>200600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>192600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>217800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>200600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>198200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>167500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>207900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>211100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>169600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>183000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>171000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>213400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>188300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>130800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>62300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>131300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>151900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>101500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>165100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>158800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>156400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>108200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>143900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>163800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>157700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>141100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>150100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>179700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>123400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>94500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F22" s="3">
         <v>26300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>26600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>26600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>28600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>18800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>20100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>21400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>27000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>12100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>9900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>10500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>5700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>5400</v>
       </c>
       <c r="R22" s="3">
         <v>5700</v>
       </c>
       <c r="S22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="T22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>6100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>7100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>6900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>6800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>7300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>8300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>9700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>10900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>11500</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>12400</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>12400</v>
       </c>
       <c r="AE22" s="3">
         <v>12400</v>
       </c>
       <c r="AF22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>13800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>12100</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>11300</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>11700</v>
       </c>
       <c r="AJ22" s="3">
         <v>11300</v>
       </c>
       <c r="AK22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AM22" s="3">
         <v>7900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>5600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>164500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>182900</v>
+      </c>
+      <c r="F23" s="3">
         <v>159100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>138800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>116900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>148100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>149400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>149300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>138700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>160600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>162100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>161600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>131100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>177500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>180500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>139300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>152000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>140100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>180400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>155900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>97800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>26300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>95500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>116600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>63100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>127300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>119500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>116300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>68000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>104200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>122700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>118100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>103500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>112900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>142500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>94600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>70400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>31300</v>
+      </c>
+      <c r="F24" s="3">
         <v>33300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>26400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>22200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>25900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>32100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>31100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>29100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>32800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>34200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>34100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>26800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>36300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>38700</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>29600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>31600</v>
       </c>
       <c r="S24" s="3">
         <v>29600</v>
       </c>
       <c r="T24" s="3">
+        <v>31600</v>
+      </c>
+      <c r="U24" s="3">
+        <v>29600</v>
+      </c>
+      <c r="V24" s="3">
         <v>38200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>31700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>20200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>7800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>8500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>24500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>11100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>24600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>25600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>24400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>14600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>16900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>27800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>26900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>33000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>41000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>30100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>20400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2727,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>151600</v>
+      </c>
+      <c r="F26" s="3">
         <v>125800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>112400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>94700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>122200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>117300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>118200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>109600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>127800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>127900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>127600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>104300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>141200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>141800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>109600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>120400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>110500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>142200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>124100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>77600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>18500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>87000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>92100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>52000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>102700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>93900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>91900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>53400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>87300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>94900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>91200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>104600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>79800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>101500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>64500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>50000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>151600</v>
+      </c>
+      <c r="F27" s="3">
         <v>125800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>112400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>94700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>122200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>117300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>118200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>109600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>127800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>127900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>127600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>104300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>141200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>141800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>109600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>120400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>110500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>142200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>124100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>77600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>18500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>87000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>92100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>52000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>102700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>93900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>91900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>53400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>87300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>94900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>91200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>104600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>79800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>101500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>64500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>50000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3084,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3033,44 +3155,44 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>-600</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>22100</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3081,8 +3203,14 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3322,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,234 +3441,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1400</v>
-      </c>
       <c r="I32" s="3">
-        <v>-1800</v>
+        <v>-5000</v>
       </c>
       <c r="J32" s="3">
         <v>-1400</v>
       </c>
       <c r="K32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>39300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>4200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>9300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>200</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>3900</v>
       </c>
       <c r="AE32" s="3">
         <v>200</v>
       </c>
       <c r="AF32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>4500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>1000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>151600</v>
+      </c>
+      <c r="F33" s="3">
         <v>125800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>112400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>94700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>122200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>117300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>118200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>109600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>127800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>127900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>127600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>104300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>141200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>141800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>109600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>120400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>110500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>142200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>124100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>77600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>18500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>87000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>92100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>52000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>102700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>93900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>91900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>48600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>86700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>94900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>91200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>126600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>79800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>101500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>64500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>50000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3798,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>151600</v>
+      </c>
+      <c r="F35" s="3">
         <v>125800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>112400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>94700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>122200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>117300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>118200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>109600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>127800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>127900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>127600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>104300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>141200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>141800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>109600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>120400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>110500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>142200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>124100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>77600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>18500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>87000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>92100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>52000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>102700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>93900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>91900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>48600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>86700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>94900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>91200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>126600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>79800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>101500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>64500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>50000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4088,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,129 +4131,137 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>108400</v>
+      </c>
+      <c r="F41" s="3">
         <v>147800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>130200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>130400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>116000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>165300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>125400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>136200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>115700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>143100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>129100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>122000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>163500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>128700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>120900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>170500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>300000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>174200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>133300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>225700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>208300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>221800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>306300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>115100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>151200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>147800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>149200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>85500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>95700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>266800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>155900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>132800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>90400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>110700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>88400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>87700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -4185,468 +4365,498 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>571600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>587800</v>
+      </c>
+      <c r="F43" s="3">
         <v>589000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>624100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>531300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>594700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>538500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>530300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>533800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>590900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>524200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>527900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>546600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>537300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>530800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>499500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>465700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>489400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>516700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>470600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>455400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>471900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>498300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>474900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>471600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>530800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>500000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>489700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>463200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>491400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>507700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>512400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>488300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>505100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>498800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>428700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>358400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>451100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>444800</v>
+      </c>
+      <c r="F44" s="3">
         <v>459300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>473700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>472200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>476900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>438200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>443600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>451200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>454800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>439700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>440200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>447700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>383400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>399600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>383200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>366400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>327200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>304000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>295800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>282400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>277000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>310600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>312100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>294800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>283400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>282600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>280700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>271200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>264500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>271400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>284400</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>275700</v>
-      </c>
-      <c r="AI44" s="3">
-        <v>264300</v>
       </c>
       <c r="AJ44" s="3">
         <v>275700</v>
       </c>
       <c r="AK44" s="3">
+        <v>264300</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>275700</v>
+      </c>
+      <c r="AM44" s="3">
         <v>275800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>241300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F45" s="3">
         <v>43700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14500</v>
       </c>
-      <c r="G45" s="3">
-        <v>6000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>12300</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3">
-        <v>12600</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="N45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>48800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>56500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>56200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>51600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>48300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>50900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>49600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>64600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>63400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>50100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>50000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>48800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>45900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>50300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>45300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>47300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>32500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>32000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>31300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>31200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>34900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>35900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>32700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1251700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1242900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1326800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1323500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1226000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1275000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1224100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1185600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1208100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1229300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1176900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1155400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1178400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1133000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1115600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1059800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1054200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1164800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1045800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>949400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1028100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1020600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1080700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1143300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>930300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1011200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>980700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>964900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>867200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>884100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1077800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>984000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>928000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>888400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>920200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>828800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>720000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10400</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -4675,11 +4885,11 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4750,234 +4960,252 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>591300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>594400</v>
+      </c>
+      <c r="F48" s="3">
         <v>605400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>633900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>626300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>638200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>498000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>492400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>499800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>499000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>455300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>462000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>472800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>455700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>459700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>463500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>473300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>466400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>473800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>482300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>481700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>480700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>547000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>526200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>530700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>398900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>392000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>386300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>387700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>386700</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>356800</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>359500</v>
       </c>
       <c r="AH48" s="3">
         <v>356800</v>
       </c>
       <c r="AI48" s="3">
+        <v>359500</v>
+      </c>
+      <c r="AJ48" s="3">
+        <v>356800</v>
+      </c>
+      <c r="AK48" s="3">
         <v>346400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>335700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>320000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>269800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4003700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3986300</v>
+      </c>
+      <c r="F49" s="3">
         <v>4004400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4026100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3946800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4021700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3414500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3425300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3471600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3456900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2461300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2474900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2484900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2134100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2157000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2179000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2210600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2070500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2089300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2104800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2119800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2120900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2137700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2028200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2045400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2060300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2072500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2078700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>2097700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>2107800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>2126600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>2148300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5317,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5436,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>72600</v>
+      </c>
+      <c r="F52" s="3">
         <v>60900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>64500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>60700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>54800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>47200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>48800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>48400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>50500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>91300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>88700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>89200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>97600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>91500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>93900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>96800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>89200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>61200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>58300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>53800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>52400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>54500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>45200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>44500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>46000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>46300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>45100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>45100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>42500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>46200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>47400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>45700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>57200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>55900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>34900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5674,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5960900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5917700</v>
+      </c>
+      <c r="F54" s="3">
         <v>6009700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6062000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5871500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6001000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5204400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5171900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5247100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5251800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4197000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4193100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>4237400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3820400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3823800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3796300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3835000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3791000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3670100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3594900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3683400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3674700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3820000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3742900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3550900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3516400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3491500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3475100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3397700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3421000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3607400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3539200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5840,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,686 +5883,724 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>121000</v>
+      </c>
+      <c r="F57" s="3">
         <v>129500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>119900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>88500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>97800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>98300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>103200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>103200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>106300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>105100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>85400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>90600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>99300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>100400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>96900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>96500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>91700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>92900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>84800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>74100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>70900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>71400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>79800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>78100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>85100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>85600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>93000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>81000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>83600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>80800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>86800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>82100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>86000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>80700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>85200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>74000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>338300</v>
+      </c>
+      <c r="F58" s="3">
         <v>359200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>118000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>122900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>126300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>118700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>141000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>138500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>137400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>132000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>625000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>443200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>397400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>407000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>316200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>39900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>40000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>37200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>44100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>44100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>44000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>49800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>49800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>49300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>174100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>173500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>158400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>58400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>33300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>38600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>231500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>331700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>331400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>132200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>145500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>46600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>107200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>99800</v>
+      </c>
+      <c r="F59" s="3">
         <v>88500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>92800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>102500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>108900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>118000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>131900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>144800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>163600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>140400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>136700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>148400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>337500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>319900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>309400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>293100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>313700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>290700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>256300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>241300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>248100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>226000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>230600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>216000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>218400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>185200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>195100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>185100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>233400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>221700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>216400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>196000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>230300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>224400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>225800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>169600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>758300</v>
+      </c>
+      <c r="F60" s="3">
         <v>783100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>516600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>484100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>528500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>518300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>536000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>551700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>582100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>528600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>990400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>825500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>834200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>827300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>722500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>429500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>445400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>420800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>385300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>359600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>363100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>347200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>360200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>343300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>477600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>444200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>446500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>324500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>350300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>341100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>534700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>609800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>647700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>437400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>456500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>290200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2008100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1754100</v>
+      </c>
+      <c r="F61" s="3">
         <v>1861600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2205500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2172300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2194100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1494400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1511500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1617400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1725500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>829200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>450100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>703400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>356500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>415200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>493200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>787900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>796700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>804800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>845000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>992100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1078400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1232100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1248300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1084400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1084900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1179900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1220400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1331400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1294200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1521400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1312500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>912400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>82600</v>
+      </c>
+      <c r="F62" s="3">
         <v>83300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>77200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>33800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>42100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>39000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>36600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>54800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>44200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>35300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>32200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>38600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>335300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>382300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>390100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>399000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>389800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>381300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>414300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>474500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>474200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>470800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>481900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>488900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>372900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>320600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>336900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>340300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>325800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>322000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>329200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>336900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>345200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>369000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>386300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>296600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6712,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6831,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6950,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2848800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2874100</v>
+      </c>
+      <c r="F66" s="3">
         <v>3027900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3101700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2994900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3068800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2350600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2383600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2523100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2653700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1617200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1696100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1790700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1526000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1624800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1605700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1616400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1631800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1606900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1644600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1826200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1915700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2050000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2090400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1916600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1935400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1944700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2003800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1996200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1970300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2184500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2176300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7116,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7231,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7350,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7469,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7588,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4688200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4600600</v>
+      </c>
+      <c r="F72" s="3">
         <v>4495000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4413300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4345200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4295200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4217700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4139300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4060100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3989400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3900400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3809600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3719300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3652200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3548200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3435800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3355700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3265000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3184200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3064700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2963300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2908700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2912800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2847800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2776700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2747700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2666800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2593000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2521100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2488400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>2403200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>2325700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7826,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7945,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8064,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3112100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3043600</v>
+      </c>
+      <c r="F76" s="3">
         <v>2981800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2960300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2876600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2932200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2853800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2788300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2724000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2598100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2579800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2497000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2446700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2294400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2199000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2190600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2218600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2159100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2063200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1950400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1857200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1759000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1769900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1652500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1634300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1581000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1546900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1471300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1401500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1450700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1422900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1362900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>962300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>893800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8302,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>151600</v>
+      </c>
+      <c r="F81" s="3">
         <v>125800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>112400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>94700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>122200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>117300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>118200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>109600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>127800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>127900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>127600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>104300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>141200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>141800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>109600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>120400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>110500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>142200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>124100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>77600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>18500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>87000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>92100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>52000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>102700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>93900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>91900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>48600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>86700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>94900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>91200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>126600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>79800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>101500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>64500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>50000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,121 +8592,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F83" s="3">
         <v>8200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>19900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>14200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>13400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>13200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>13100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>12600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>12200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>12200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>12400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>12300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>24700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>24900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>25000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>25400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>25700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>26900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>25300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>26000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>29100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>28500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>27000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>28600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>26900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>27800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>27700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>27700</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>27400</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>27300</v>
       </c>
       <c r="AG83" s="3">
         <v>27400</v>
       </c>
       <c r="AH83" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>27400</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>26300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>25500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>26000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>20900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>18500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8826,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8945,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9064,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9183,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9302,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>140400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>202900</v>
+      </c>
+      <c r="F89" s="3">
         <v>238000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>119200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>159100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>96400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>164800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>122600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>172400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>163200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>190200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>164600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>123300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>173400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>125200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>96400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>118100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>170500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>127700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>104400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>143300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>192500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>91800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>101900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>116300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>146500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>74500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>105100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>56800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>161700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>130600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>103000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>109300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>135000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>82400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>58200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>81200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,121 +9468,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-11600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-16000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-21400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-20600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-21900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-14400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-7500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-8900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-6000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-9300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-12100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-12300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-12500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-10200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-9300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-10800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-7900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-14400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9702,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +9821,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-17600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-12800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-14300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-809500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-19700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-9500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-5700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1034900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-6000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-387100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-12200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-12300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-184100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-10200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-9300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-5800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-30900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-135500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-18400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-32200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-48900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-22100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,121 +9987,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>46100</v>
+      </c>
+      <c r="F96" s="3">
         <v>44100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>44300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>44600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>44600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>39000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>38900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>38900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>38800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>37100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>37300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>37200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-37200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-29600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-29700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-29700</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-22700</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-22700</v>
       </c>
       <c r="V96" s="3">
         <v>-22700</v>
       </c>
       <c r="W96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-22600</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-21900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-22000</v>
       </c>
       <c r="Z96" s="3">
         <v>-21900</v>
       </c>
       <c r="AA96" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-21800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-17300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-15500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10221,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10340,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,343 +10459,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-112200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-261900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-203700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-113200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-127600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>665100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-104900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-125300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-140500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>852600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-166900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-150900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>215700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-121600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-101500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-131000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-61900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-34800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-77800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-188100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-122300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-176100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-44400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>107200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-138200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-121500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-31300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-280200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>749100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-5600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-8400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>6600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-4900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-2800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>4300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>3600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>2200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>4900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>3200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F102" s="3">
         <v>17600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>14500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-49400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>39900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>20500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-27500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>14100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-41500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>34700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>7800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-49600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-129400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>125700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>40900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-92400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>17400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-13500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-84500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>191200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-36100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>3300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>63600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-171100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>110900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>23100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>42500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>22300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>20400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NDSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>NDSN</t>
   </si>
@@ -656,531 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43131</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43039</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42947</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42766</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>740800</v>
+      </c>
+      <c r="E8" s="3">
         <v>669500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>751800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>741500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>682900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>615400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>744500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>661600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>650600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>633200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>719300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>648700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>650200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>610500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>683600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>662100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>635400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>609200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>599200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>646900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>589500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>526600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>558500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>538200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>529500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>494900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>585500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>559700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>551100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>497900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>569300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>581200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>553700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>550400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>573900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>589400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>496100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>407500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>509300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>336800</v>
+      </c>
+      <c r="E9" s="3">
         <v>303300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>325200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>335000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>309000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>279500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>334000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>292600</v>
-      </c>
-      <c r="K9" s="3">
-        <v>284800</v>
       </c>
       <c r="L9" s="3">
         <v>284800</v>
       </c>
       <c r="M9" s="3">
+        <v>284800</v>
+      </c>
+      <c r="N9" s="3">
         <v>335200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>288400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>298000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>281600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>320400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>296500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>277800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>269000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>268100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>281600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>251800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>236600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>261700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>257400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>239900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>231700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>266500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>257100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>249600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>228900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>261400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>260800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>246700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>249500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>261900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>263200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>220600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>182300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>404100</v>
+      </c>
+      <c r="E10" s="3">
         <v>366100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>426600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>406500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>373900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>335900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>410500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>369000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>365900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>348400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>384100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>360300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>352100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>328900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>363200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>365600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>357600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>340200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>331100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>365300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>337700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>290000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>296800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>280800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>289600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>263200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>319000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>302600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>301500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>269000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>307900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>320400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>307000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>300900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>312000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>326200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>275500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>225200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,19 +1234,20 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>68200</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1242,11 +1255,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>65000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1254,11 +1267,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>71400</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1341,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,31 +1476,34 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>7700</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1504,23 +1523,23 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1528,11 +1547,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>87400</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1543,89 +1562,92 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>1200</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>200</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E15" s="3">
         <v>36600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>37800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>37600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>33400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>31300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>27100</v>
       </c>
       <c r="O15" s="3">
         <v>27100</v>
       </c>
       <c r="P15" s="3">
+        <v>27100</v>
+      </c>
+      <c r="Q15" s="3">
         <v>26400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1698,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>566600</v>
+      </c>
+      <c r="E17" s="3">
         <v>502100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>532600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>540000</v>
       </c>
-      <c r="G17" s="3">
-        <v>513200</v>
-      </c>
       <c r="H17" s="3">
+        <v>512700</v>
+      </c>
+      <c r="I17" s="3">
         <v>473500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>556400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>493000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>481000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>472700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>529600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>476300</v>
       </c>
       <c r="O17" s="3">
         <v>476300</v>
       </c>
       <c r="P17" s="3">
+        <v>476300</v>
+      </c>
+      <c r="Q17" s="3">
         <v>464900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>506000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>477200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>451400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>453300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>447800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>458600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>423100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>417500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>521200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>426100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>404400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>419800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>445800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>429500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>422200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>413600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>452500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>443700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>422300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>431100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>449200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>436000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>392600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>331600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>397200</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>174200</v>
+      </c>
+      <c r="E18" s="3">
         <v>167300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>219200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>201500</v>
       </c>
-      <c r="G18" s="3">
-        <v>169800</v>
-      </c>
       <c r="H18" s="3">
+        <v>170300</v>
+      </c>
+      <c r="I18" s="3">
         <v>142000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>188100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>168600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>169600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>160500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>189700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>172300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>173800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>145600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>177600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>184900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>184000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>155900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>151400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>188300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>166400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>109100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>37300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>112100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>125100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>75100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>139700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>130200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>128900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>84300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>116800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>137500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>131400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>119300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>124800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>153400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>103500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>75900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,332 +2051,339 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-39300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E21" s="3">
         <v>223800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>248200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>234900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>202400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>179500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>219600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>200600</v>
       </c>
       <c r="K21" s="3">
         <v>200600</v>
       </c>
       <c r="L21" s="3">
+        <v>200600</v>
+      </c>
+      <c r="M21" s="3">
         <v>192600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>217800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>200600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>198200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>167500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>207900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>211100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>169600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>183000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>171000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>213400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>188300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>130800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>62300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>131300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>151900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>101500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>165100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>158800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>156400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>108200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>143900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>163800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>157700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>141100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>150100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>179700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>123400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>94500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E22" s="3">
         <v>23100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>24800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>26600</v>
       </c>
       <c r="H22" s="3">
         <v>26600</v>
       </c>
       <c r="I22" s="3">
+        <v>26600</v>
+      </c>
+      <c r="J22" s="3">
         <v>28600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>5700</v>
       </c>
       <c r="R22" s="3">
         <v>5700</v>
       </c>
       <c r="S22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="T22" s="3">
         <v>5400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11500</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>12400</v>
       </c>
       <c r="AF22" s="3">
         <v>12400</v>
@@ -2353,269 +2392,278 @@
         <v>12400</v>
       </c>
       <c r="AH22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>13800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>11300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>11700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>11300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>7900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>5600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E23" s="3">
         <v>164500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>182900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>159100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>138800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>116900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>148100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>149400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>149300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>138700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>160600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>162100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>161600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>131100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>177500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>180500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>139300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>152000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>140100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>180400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>155900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>97800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>95500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>116600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>63100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>127300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>119500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>116300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>68000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>104200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>122700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>118100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>103500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>112900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>142500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>94600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>70400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E24" s="3">
         <v>31100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>34200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>34100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>36300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>38700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>31600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>38200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>20200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>24500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>24600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>25600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>24400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>16900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>27800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>33000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>41000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>30100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>20400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E26" s="3">
         <v>133400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>151600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>125800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>112400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>94700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>122200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>117300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>118200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>109600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>127800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>127900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>127600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>104300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>141200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>141800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>109600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>120400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>110500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>142200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>124100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>77600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>87000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>92100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>52000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>102700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>93900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>91900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>53400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>87300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>94900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>91200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>104600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>79800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>101500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>64500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>50000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E27" s="3">
         <v>133400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>151600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>125800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>112400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>94700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>122200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>117300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>118200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>109600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>127800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>127900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>127600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>104300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>141200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>141800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>109600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>120400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>110500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>142200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>124100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>77600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>87000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>92100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>52000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>102700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>93900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>91900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>53400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>87300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>94900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>91200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>104600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>79800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>101500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>64500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>50000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3161,8 +3221,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3170,8 +3230,8 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3180,22 +3240,22 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-600</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>22100</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3209,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E32" s="3">
         <v>19900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
-        <v>500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>39300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>9300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E33" s="3">
         <v>133400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>151600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>125800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>112400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>94700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>122200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>117300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>118200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>109600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>127800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>127900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>127600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>104300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>141200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>141800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>109600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>120400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>110500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>142200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>124100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>77600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>87000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>92100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>52000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>102700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>93900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>91900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>48600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>86700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>94900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>91200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>126600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>79800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>101500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>64500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>50000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E35" s="3">
         <v>133400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>151600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>125800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>112400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>94700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>122200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>117300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>118200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>109600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>127800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>127900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>127600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>104300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>141200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>141800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>109600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>120400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>110500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>142200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>124100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>77600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>87000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>92100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>52000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>102700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>93900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>91900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>48600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>86700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>94900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>91200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>126600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>79800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>101500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>64500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>50000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43131</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43039</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42947</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42766</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,139 +4218,143 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E41" s="3">
         <v>120400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>147800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>130200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>130400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>116000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>165300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>125400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>136200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>115700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>143100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>129100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>122000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>163500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>128700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>120900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>170500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>174200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>133300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>225700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>208300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>221800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>306300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>115100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>151200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>147800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>149200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>85500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>95700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>266800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>155900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>132800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>90400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>110700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>88400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>87700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4371,495 +4460,510 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>606700</v>
+      </c>
+      <c r="E43" s="3">
         <v>571600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>587800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>589000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>624100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>531300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>594700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>538500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>530300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>533800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>590900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>524200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>527900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>546600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>537300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>530800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>499500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>465700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>489400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>516700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>470600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>455400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>471900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>498300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>474900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>471600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>530800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>500000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>489700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>463200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>491400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>507700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>512400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>488300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>505100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>498800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>428700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>358400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>857100</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>467800</v>
+      </c>
+      <c r="E44" s="3">
         <v>451100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>444800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>459300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>473700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>472200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>476900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>438200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>443600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>451200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>454800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>439700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>440200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>447700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>383400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>399600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>383200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>366400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>327200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>304000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>295800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>282400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>277000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>310600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>312100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>294800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>283400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>282600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>280700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>271200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>264500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>271400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>284400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>275700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>264300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>275700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>275800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>241300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E45" s="3">
         <v>18500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12300</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12600</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>48800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>56500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>56200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>50900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>49600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>64600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>63400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>50100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>50000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>45900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>50300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>45300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>47300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>32500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>32000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>31300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>31200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>28600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>34900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>35900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>32700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1277400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1251700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1242900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1326800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1323500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1226000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1275000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1224100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1185600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1208100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1229300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1176900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1155400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1178400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1133000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1115600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1059800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1054200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1164800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1045800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>949400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1028100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1020600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1080700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1143300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>930300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1011200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>980700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>964900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>867200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>884100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1077800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>984000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>928000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>888400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>920200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>828800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>720000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E47" s="3">
         <v>7700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10400</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -4891,8 +4995,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4966,246 +5070,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>587200</v>
+      </c>
+      <c r="E48" s="3">
         <v>591300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>594400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>605400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>633900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>626300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>638200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>498000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>492400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>499800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>499000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>455300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>462000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>472800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>455700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>459700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>463500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>473300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>466400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>473800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>482300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>481700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>480700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>547000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>526200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>530700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>398900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>392000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>386300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>387700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>386700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>356800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>359500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>356800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>346400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>335700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>320000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>269800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>546300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3983900</v>
+      </c>
+      <c r="E49" s="3">
         <v>4003700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3986300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4004400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4026100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3946800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4021700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3414500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3425300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3471600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3456900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2461300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2474900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2484900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2134100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2157000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2179000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2210600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2070500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2089300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2104800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2119800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2120900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2137700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2028200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2045400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2060300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2072500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2078700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2097700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2107800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2126600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2148300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2170100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2136400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2147500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2174500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1368400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1367400</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E52" s="3">
         <v>95200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>72600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>60900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>64500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>60700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>47200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>91300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>88700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>89200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>97600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>91500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>93900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>96800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>89200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>58300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>53800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>52400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>54500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>45200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>44500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>46000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>46300</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>45100</v>
       </c>
       <c r="AF52" s="3">
         <v>45100</v>
       </c>
       <c r="AG52" s="3">
+        <v>45100</v>
+      </c>
+      <c r="AH52" s="3">
         <v>42500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>46200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>45700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>43400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>57200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>55900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>34900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5964400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5960900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5917700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6009700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6062000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5871500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6001000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5204400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5171900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5247100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5251800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4197000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4193100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4237400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3820400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3823800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3796300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3835000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3791000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3670100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3594900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3683400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3674700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3820000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3742900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3550900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3516400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3491500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3475100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3397700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3421000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3607400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3539200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3500600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3414500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3460500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3379200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2393000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2420600</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E57" s="3">
         <v>117700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>121000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>129500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>119900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>88500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>97800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>98300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>103200</v>
       </c>
       <c r="L57" s="3">
         <v>103200</v>
       </c>
       <c r="M57" s="3">
+        <v>103200</v>
+      </c>
+      <c r="N57" s="3">
         <v>106300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>105100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>85400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>90600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>99300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>96900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>96500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>91700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>92900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>84800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>74100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>70900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>71400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>79800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>78100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>85100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>85600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>93000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>81000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>83600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>80800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>86800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>82100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>86000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>80700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>85200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>74000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E58" s="3">
         <v>76500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>338300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>359200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>118000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>122900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>126300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>118700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>141000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>138500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>137400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>132000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>625000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>443200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>397400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>407000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>316200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>39900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>40000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>37200</v>
-      </c>
-      <c r="W58" s="3">
-        <v>44100</v>
       </c>
       <c r="X58" s="3">
         <v>44100</v>
       </c>
       <c r="Y58" s="3">
+        <v>44100</v>
+      </c>
+      <c r="Z58" s="3">
         <v>44000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>49800</v>
       </c>
       <c r="AA58" s="3">
         <v>49800</v>
       </c>
       <c r="AB58" s="3">
+        <v>49800</v>
+      </c>
+      <c r="AC58" s="3">
         <v>49300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>174100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>173500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>158400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>58400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>33300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>38600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>231500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>331700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>331400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>132200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>145500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>46600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>107200</v>
+        <v>107000</v>
       </c>
       <c r="E59" s="3">
+        <v>108700</v>
+      </c>
+      <c r="F59" s="3">
         <v>99800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>88500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>92800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>102500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>108900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>118000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>131900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>144800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>163600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>140400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>136700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>148400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>337500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>319900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>309400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>293100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>313700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>290700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>256300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>241300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>248100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>226000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>230600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>216000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>218400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>185200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>195100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>185100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>233400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>221700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>216400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>196000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>230300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>224400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>225800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>169600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>374500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>491900</v>
+      </c>
+      <c r="E60" s="3">
         <v>460000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>758300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>783100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>516600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>484100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>528500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>518300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>536000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>551700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>582100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>528600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>990400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>825500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>834200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>827300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>722500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>429500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>445400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>420800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>385300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>359600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>363100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>347200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>360200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>343300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>477600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>444200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>446500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>324500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>350300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>341100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>534700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>609800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>647700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>437400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>456500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>290200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>331500</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1898500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2008100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1754100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1861600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2205500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2172300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2194100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1494400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1511500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1617400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1725500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>829200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>450100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>703400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>356500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>415200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>493200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>787900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>796700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>804800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>845000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>992100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1078400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1232100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1248300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1084400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1084900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1179900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1220400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1331400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1294200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1521400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1312500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1258800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1266100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1569700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1574200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>912400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>942800</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E62" s="3">
         <v>97900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>83300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>77200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>36600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>335300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>382300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>390100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>399000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>389800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>381300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>414300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>474500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>474200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>470800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>481900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>488900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>372900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>320600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>336900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>340300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>325800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>322000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>329200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>336900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>345200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>369000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>386300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>296600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>294700</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2762200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2848800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2874100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3027900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3101700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2994900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3068800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2350600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2383600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2523100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2653700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1617200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1696100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1790700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1526000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1624800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1605700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1616400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1631800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1606900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1644600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1826200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1915700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2050000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2090400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1916600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1935400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1944700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2003800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1996200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1970300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2184500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2176300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2205500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2259000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2376100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2417000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1499200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1569000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4759700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4688200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4600600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4495000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4413300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4345200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4295200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4217700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4139300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4060100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3989400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3900400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3809600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3719300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3652200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3548200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3435800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3355700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3265000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3184200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3064700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2963300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2908700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2912800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2847800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2776700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2747700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2666800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2593000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2521100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2488400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2403200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2325700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2251800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2164600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2102100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2016100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1967100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1932600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3202200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3112100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3043600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2981800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2960300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2876600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2932200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2853800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2788300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2724000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2598100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2579800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2497000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2446700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2294400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2199000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2190600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2218600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2159100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2063200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1950400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1857200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1759000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1769900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1652500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1634300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1581000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1546900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1471300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1401500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1450700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1422900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1362900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1295100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1155500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1084400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>962300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>893800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>851600</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43131</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43039</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42947</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42766</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E81" s="3">
         <v>133400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>151600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>125800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>112400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>94700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>122200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>117300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>118200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>109600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>127800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>127900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>127600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>104300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>141200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>141800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>109600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>120400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>110500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>142200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>124100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>77600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>87000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>92100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>52000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>102700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>93900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>91900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>48600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>86700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>94900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>91200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>126600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>79800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>101500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>64500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>50000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E83" s="3">
         <v>17700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>12200</v>
       </c>
       <c r="N83" s="3">
         <v>12200</v>
       </c>
       <c r="O83" s="3">
+        <v>12200</v>
+      </c>
+      <c r="P83" s="3">
         <v>12400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>25400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>26900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>26000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>29100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>28500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>28600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>26900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>27800</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>27700</v>
       </c>
       <c r="AF83" s="3">
         <v>27700</v>
       </c>
       <c r="AG83" s="3">
+        <v>27700</v>
+      </c>
+      <c r="AH83" s="3">
         <v>27400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>27300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>27400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>26300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>25500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>26000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>20900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>18500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E89" s="3">
         <v>140400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>202900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>238000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>119200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>159100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>96400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>164800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>122600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>172400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>163200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>190200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>164600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>123300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>173400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>125200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>96400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>118100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>170500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>127700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>104400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>143300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>192500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>91800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>101900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>116300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>146500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>74500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>105100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>161700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>130600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>103000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>109300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>135000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>82400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>58200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>81200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-809500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1034900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-387100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-184100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-135500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-32200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-48900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-59900</v>
-      </c>
-      <c r="AK94" s="3">
-        <v>-22100</v>
       </c>
       <c r="AL94" s="3">
         <v>-22100</v>
       </c>
       <c r="AM94" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-810600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-57800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,67 +10221,68 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E96" s="3">
         <v>45800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>46100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>44100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>44300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>44600</v>
       </c>
       <c r="I96" s="3">
         <v>44600</v>
       </c>
       <c r="J96" s="3">
+        <v>44600</v>
+      </c>
+      <c r="K96" s="3">
         <v>39000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>38900</v>
       </c>
       <c r="L96" s="3">
         <v>38900</v>
       </c>
       <c r="M96" s="3">
+        <v>38900</v>
+      </c>
+      <c r="N96" s="3">
         <v>38800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>37100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>37300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>37200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-37200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-29400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-29600</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-29700</v>
       </c>
       <c r="U96" s="3">
         <v>-29700</v>
       </c>
       <c r="V96" s="3">
-        <v>-22700</v>
+        <v>-29700</v>
       </c>
       <c r="W96" s="3">
         <v>-22700</v>
@@ -10058,58 +10291,61 @@
         <v>-22700</v>
       </c>
       <c r="Y96" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-22600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-21900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-21800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-20100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-20200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-20300</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-17400</v>
       </c>
       <c r="AI96" s="3">
         <v>-17400</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-17300</v>
+        <v>-17400</v>
       </c>
       <c r="AK96" s="3">
         <v>-17300</v>
       </c>
       <c r="AL96" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-15600</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-15500</v>
       </c>
       <c r="AN96" s="3">
         <v>-15500</v>
       </c>
       <c r="AO96" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-176600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-112200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-261900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-203700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-113200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-127600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>665100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-104900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-125300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-140500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>852600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-166900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-150900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>215700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-121600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-101500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-131000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-61900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-34800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-77800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-188100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-122300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-176100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-44400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>107200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-138200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-121500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-43000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-31300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-280200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-130400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-35600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>749100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-35200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-69100</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-27500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-49600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-129400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>125700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>40900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-92400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>17400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-84500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>191200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-36100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>63600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-171100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>110900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>42500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>20400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>6900</v>
       </c>
     </row>
